--- a/workspaces/btc_daily_14days/roc/roc_7.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_7.xlsx
@@ -575,46 +575,46 @@
         <v>19</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-10.38817516231284</v>
+        <v>-10.35580089526676</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.055130136261724</v>
+        <v>9.025914812532065</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.396669179776957</v>
+        <v>3.384884826407756</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.794903365919822</v>
+        <v>8.766146775547575</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.258132480806069</v>
+        <v>8.231201465656049</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.981356511813637</v>
+        <v>-1.975301957696637</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.337663414157063</v>
+        <v>-7.314384823328048</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.535134046212207</v>
+        <v>-2.527354302058711</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.676399566313947</v>
+        <v>2.667971485997377</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.449571150247408</v>
+        <v>-3.438736190710458</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>12.17252477401216</v>
+        <v>12.13368800391666</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.2102628452805</v>
+        <v>12.1709917923768</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.79169896386197</v>
+        <v>11.75386887504725</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>17.32505450265867</v>
+        <v>17.26965810889358</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>16</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.493438320212817</v>
+        <v>-2.486032928832174</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-10.35752081074286</v>
+        <v>-10.32490540237625</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-10.75501475056137</v>
+        <v>-10.72164303043701</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.372651986248279</v>
+        <v>-4.359545910220099</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.912651089479425</v>
+        <v>-4.897693395925273</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-10.8738934390669</v>
+        <v>-10.83934813724281</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.702287118945968</v>
+        <v>-4.68723611511782</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.171288565511254</v>
+        <v>-5.155011330628277</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.29078858892408</v>
+        <v>7.267530978444803</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1768142145296423</v>
+        <v>0.1761451676317591</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.02828492808957606</v>
+        <v>-0.0284375065038347</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.260486024981418</v>
+        <v>-6.241025159442273</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.683592608928613</v>
+        <v>-6.662663844764772</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1646115673532904</v>
+        <v>-0.1645524174274442</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>33</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.112622285852012</v>
+        <v>8.085921545358886</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.533745685616374</v>
+        <v>9.50262391406293</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.141155624227551</v>
+        <v>9.110783544598284</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.208709727822054</v>
+        <v>3.197531204503875</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.703885863754188</v>
+        <v>5.684795428982646</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.968868790726269</v>
+        <v>2.959201992057757</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-6.219781230549657</v>
+        <v>-6.199654601065788</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-9.724754949571832</v>
+        <v>-9.693598585847667</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.71572427999147</v>
+        <v>-3.703777266363161</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.50554333249876</v>
+        <v>1.500582057962767</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.812741705328378</v>
+        <v>-7.787797443030854</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.335795414468485</v>
+        <v>1.331000804734629</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-5.164153732065181</v>
+        <v>-5.147869609755816</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.8746713262681</v>
+        <v>-1.869097871968684</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>62</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.345271357210109</v>
+        <v>2.336817214129368</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.960551637802688</v>
+        <v>3.946934892527892</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.02147632012695</v>
+        <v>9.987494790470308</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>11.76851450633954</v>
+        <v>11.72903889943739</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.159918756918458</v>
+        <v>3.148701869020762</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.386478687939082</v>
+        <v>-1.382114964856804</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.758819240100507</v>
+        <v>1.753301089654649</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.3244172768567424</v>
+        <v>-0.3232973199797513</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.001791504381835</v>
+        <v>-1.995170979368744</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.237641180804069</v>
+        <v>-1.233738455947616</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.060271938127627</v>
+        <v>-3.050293016396715</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.408759964046169</v>
+        <v>-1.404682097207491</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.4486731596837</v>
+        <v>-3.437616809622348</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-8.053395063964793</v>
+        <v>-8.02745564323105</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>70</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7.506561679789698</v>
+        <v>7.480617095407148</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.677059562367006</v>
+        <v>-2.669011811430494</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2140104487469543</v>
+        <v>-0.2150238332549961</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.205401370553837</v>
+        <v>4.189800043305233</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.237430443812315</v>
+        <v>2.228908868444123</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.257164556915313</v>
+        <v>8.229530497756414</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8.174305373377635</v>
+        <v>8.14721550098561</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.414992968082466</v>
+        <v>3.403686130374886</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.4916646451766269</v>
+        <v>0.4901977290002861</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.223883084707332</v>
+        <v>-3.213227461277654</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.86238757674441</v>
+        <v>-4.846063854764949</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-7.693885132398677</v>
+        <v>-7.668718828223668</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-8.117762898995544</v>
+        <v>-8.090768701545059</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.569279880027352</v>
+        <v>-3.557409560282402</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>80</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.506561679789741</v>
+        <v>2.49661403581058</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.106029375357075</v>
+        <v>-4.092802626982966</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.501963614183296</v>
+        <v>-4.488424280503644</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.874587389445132</v>
+        <v>-6.853094566223767</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.912810903735192</v>
+        <v>-4.897333813862872</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-9.62296426134057</v>
+        <v>-9.590834821607331</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-7.206504868252544</v>
+        <v>-7.182315407587701</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-10.18111086047129</v>
+        <v>-10.14659222066172</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-10.24507093219042</v>
+        <v>-10.21005682085913</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-13.60577556956612</v>
+        <v>-13.55937048388041</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-12.56160709473049</v>
+        <v>-12.51844085651355</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-15.03729582486866</v>
+        <v>-14.98615065037197</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-17.97112287824097</v>
+        <v>-17.90953632232264</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-21.48786833872077</v>
+        <v>-21.41455241742403</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>86</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-7.144601110907914</v>
+        <v>-7.121390263355231</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.6167680573962215</v>
+        <v>-0.6151012332071772</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.175228577613105</v>
+        <v>-2.169187911872832</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.045346545228256</v>
+        <v>-2.039711333769283</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2568722071292555</v>
+        <v>-0.2569168114570175</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.862338191031867</v>
+        <v>5.841983580178692</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.120332320789089</v>
+        <v>1.116607096669846</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.147249291283394</v>
+        <v>4.133418014711822</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.921715549202951</v>
+        <v>2.912445814316378</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.9045143030422125</v>
+        <v>0.9024645081383156</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6991745363452893</v>
+        <v>0.6980920960254551</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.598467479295365</v>
+        <v>-1.591836142379137</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.3118502102483447</v>
+        <v>0.312522121853462</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.6044682090118343</v>
+        <v>-0.6005989290525093</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>124</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-4.91279315891947</v>
+        <v>-4.896269077402955</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.8794139125119855</v>
+        <v>-0.8767043101516663</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.69525454063902</v>
+        <v>-3.683388701124663</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-5.180060227181499</v>
+        <v>-5.162808763015597</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.160268234777028</v>
+        <v>3.147915543842231</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.651294407965281</v>
+        <v>2.641319049440064</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.566947712127963</v>
+        <v>2.557796366913969</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.940641372141435</v>
+        <v>-1.93335408623458</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.235564571636239</v>
+        <v>-5.215998296205662</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-8.514985688828283</v>
+        <v>-8.483234086789153</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.105592679895544</v>
+        <v>-7.078632277737853</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-11.11767224380205</v>
+        <v>-11.07637546569742</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-5.06991635838515</v>
+        <v>-5.049825037686631</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-7.249026164084363</v>
+        <v>-7.221004030328196</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>167</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.990444308233926</v>
+        <v>-3.97600620619415</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.207710628447813</v>
+        <v>-3.195980883306838</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.189599866794815</v>
+        <v>1.184024478310953</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6.714263134773688</v>
+        <v>6.688062369014126</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.779427404863867</v>
+        <v>3.763692866042248</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.51814462424543</v>
+        <v>-2.509444444551853</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.8044194189113014</v>
+        <v>-0.8016146992848689</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.073273854992152</v>
+        <v>-3.061094085066507</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.7351072261051499</v>
+        <v>-0.7308799455457802</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.989851662458612</v>
+        <v>-3.972502333480385</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.196636611042592</v>
+        <v>-4.178381103415276</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-4.764612657939708</v>
+        <v>-4.743813240330923</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-5.187791912895435</v>
+        <v>-5.16555741574215</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.939215645405504</v>
+        <v>-4.91754642940051</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.208316065755035</v>
+        <v>3.210409402508603</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.597223844540785</v>
+        <v>1.598239644753271</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.202845122710329</v>
+        <v>1.203869989123191</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.178153603711799</v>
+        <v>-2.179214685558897</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.9611421477231801</v>
+        <v>-0.9613857870323628</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.289404670833775</v>
+        <v>3.291630697041597</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.1295103213272881</v>
+        <v>0.1296121069318446</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.218481156047147</v>
+        <v>-1.219483672759686</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.9180196093588435</v>
+        <v>0.9183341559245477</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.263703652693891</v>
+        <v>2.264646012193687</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.7387246029657106</v>
+        <v>0.7386366187724107</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.3326063597353937</v>
+        <v>0.3321609549711795</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.231376883901682</v>
+        <v>1.231537568970374</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.734796341067359</v>
+        <v>1.73522731825831</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2740893550666925</v>
+        <v>0.2760210652319302</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.813972583366585</v>
+        <v>1.821493577155152</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.880418261257482</v>
+        <v>0.885834933116783</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4661448435136037</v>
+        <v>-0.4662223210503811</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4752728396472463</v>
+        <v>0.4794418160242984</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.250101106990712</v>
+        <v>2.260505865567197</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.277123214933674</v>
+        <v>3.290420895087259</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.446677757822115</v>
+        <v>2.454821644304616</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.495900113183069</v>
+        <v>3.508304588081259</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.132233984966241</v>
+        <v>4.145902626181673</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.560319153256337</v>
+        <v>3.571065975347508</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.3754221706007</v>
+        <v>1.376690545976452</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.2160719155551831</v>
+        <v>0.213049670373465</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.686612756869707</v>
+        <v>2.693254274025215</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3770362038078616</v>
+        <v>-0.3769277951200323</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.1277922996299452</v>
+        <v>0.127480741137326</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.055674915784735</v>
+        <v>1.054249605571762</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.6572571053571323</v>
+        <v>0.6563044954083423</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3837695133547925</v>
+        <v>0.3828681583508384</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.20723831487814</v>
+        <v>3.203964249000933</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.329882665733372</v>
+        <v>2.327574003098768</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.249542784594134</v>
+        <v>4.246069547104703</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.804477003879079</v>
+        <v>1.803021512794068</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.6901912343843435</v>
+        <v>0.689951310029528</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4855110075876112</v>
+        <v>0.4856408567161239</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.0110904064033619</v>
+        <v>-0.01019048651780707</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.0988399184856803</v>
+        <v>0.0996519797420774</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4475292381641154</v>
+        <v>-0.4463826561513926</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.038892865664522</v>
+        <v>-2.046158271799072</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.195921024083219</v>
+        <v>-3.207629489060594</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.772607912498103</v>
+        <v>-1.776373893076375</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.0707410911000963</v>
+        <v>0.07346971080962561</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.1105656587033792</v>
+        <v>0.1142810816213782</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2766470624945825</v>
+        <v>-0.2731755778828884</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.09577852858884484</v>
+        <v>0.0991216472860188</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5419667247283471</v>
+        <v>0.5456020949383458</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7099114164250224</v>
+        <v>0.7132821087956671</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.09148439162763822</v>
+        <v>0.09035711528594703</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.254529526640376</v>
+        <v>1.256930009739897</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.8342113680320651</v>
+        <v>0.8328053970029856</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.002332683652952</v>
+        <v>1.001630140459341</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.111063790328501</v>
+        <v>0.1071867130102291</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>404</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.483537330110991</v>
+        <v>-3.470909617314959</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.382239655946599</v>
+        <v>-1.376320922661591</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.04443509521639299</v>
+        <v>-0.04652024182946946</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.141904734886147</v>
+        <v>-2.137047235752867</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.690226940057272</v>
+        <v>-1.687835917851565</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.145260249866304</v>
+        <v>-1.145862264958559</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.220855898462844</v>
+        <v>-2.216278369923565</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.185388366760051</v>
+        <v>-3.176200908794669</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.99233048865608</v>
+        <v>-3.979469560103354</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.367274605464488</v>
+        <v>-2.357529224250477</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.574558245001938</v>
+        <v>-2.563725561766866</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.786340678602322</v>
+        <v>-3.768771614003569</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.46918315936464</v>
+        <v>-2.456352957621732</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.963972780360791</v>
+        <v>-2.949205882771189</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>325</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.416515243286867</v>
+        <v>-1.406175669282995</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.8742427024049633</v>
+        <v>-0.8674171868412373</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.115265255155407</v>
+        <v>-3.105249536286266</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.138858276394096</v>
+        <v>-1.135773978322234</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.677279491466265</v>
+        <v>-1.67369636439556</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.302914476827517</v>
+        <v>-2.298858613351626</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.465191390162076</v>
+        <v>-1.461470675326822</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.242758061677954</v>
+        <v>-2.232824809134158</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.614967430409806</v>
+        <v>-2.601310912332757</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.2315974049141118</v>
+        <v>0.235266301405666</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.136727042603219</v>
+        <v>-2.12212196218568</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.980486046928192</v>
+        <v>0.9867500920132386</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.3670784934833335</v>
+        <v>-0.3565814420085829</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.355050373745392</v>
+        <v>2.354678351806172</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.981381823674923</v>
+        <v>4.012455325710704</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.650383750279047</v>
+        <v>1.657616347373292</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.6221827980442</v>
+        <v>-1.639844556537845</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.4127929747892267</v>
+        <v>-0.4148274513501562</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.390063110724739</v>
+        <v>-2.412323839696576</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.250894554303962</v>
+        <v>-4.290682068405495</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-5.579160666290861</v>
+        <v>-5.645410878552362</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.966892304978764</v>
+        <v>-5.038169164126046</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-5.182356893771413</v>
+        <v>-5.265291656280382</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.380601397224837</v>
+        <v>-4.453031403856365</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.500561900557535</v>
+        <v>-3.57158964403326</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.886917441602293</v>
+        <v>-2.959347605909272</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.501760439396648</v>
+        <v>-1.554784698605992</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.260206876700579</v>
+        <v>-1.305063366329748</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-6.300544919194749</v>
+        <v>-6.374880083689298</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-10.45018959814891</v>
+        <v>-10.5670545078174</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-12.87551515753738</v>
+        <v>-13.00862241929013</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-12.74526202492981</v>
+        <v>-12.87378644027667</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-10.23799796081411</v>
+        <v>-10.34078399411283</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-10.44817023629653</v>
+        <v>-10.55157972281184</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-9.010061313974852</v>
+        <v>-9.111600440840292</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-5.633815093149188</v>
+        <v>-5.712039977817774</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.674592137599973</v>
+        <v>-4.752444478467353</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-6.536767484719398</v>
+        <v>-6.631421551023301</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-7.448823429576173</v>
+        <v>-7.560453578152703</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-7.914783377630037</v>
+        <v>-8.038890933627783</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-6.813104237455882</v>
+        <v>-6.920684006111145</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.048720261859266</v>
+        <v>-5.132501135373261</v>
       </c>
     </row>
     <row r="23">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.189</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4087~4100</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4087</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.2251456372831413</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.174</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4068~4081</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4068</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.1778294008274699</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.159</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4052~4065</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4052</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.1687150729774984</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.144</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4019~4032</t>
-        </is>
+      <c r="B9" t="n">
+        <v>4019</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.2364938757655324</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.129</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3957~3970</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3957</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.2768136350714414</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.1141</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3887~3900</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3887</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.4165152432869021</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.09909</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3807~3820</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3807</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.4777315139272531</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.08411</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3721~3734</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3721</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.3241828301189145</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.06913</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3597~3610</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3597</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.1665685141157951</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.05415</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3430~3443</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3430</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.0189055659358317</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.03917</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3203~3215</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3203</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.2072796887947419</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.02419</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2934~2944</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2934</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.2515904941230218</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.009211</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2557~2566</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2557</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.2331109624547096</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.005769</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2120~2126</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2120</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>0.1406162423488198</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.02075</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1716~1722</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1716</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.9908822372813191</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.03573</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1391~1397</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1391</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.55094249582438</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.05071</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1117~1119</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1117</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.9471336190214785</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.06569</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>922~922</t>
-        </is>
+      <c r="B23" t="n">
+        <v>922</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>2.495715692805206</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.08066</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>757~757</t>
-        </is>
+      <c r="B24" t="n">
+        <v>757</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>2.856627729988176</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.09564</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>604~604</t>
-        </is>
+      <c r="B25" t="n">
+        <v>604</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>3.135700752637703</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.1106</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>514~514</t>
-        </is>
+      <c r="B26" t="n">
+        <v>514</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>4.705005259556557</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.1256</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>425~425</t>
-        </is>
+      <c r="B27" t="n">
+        <v>425</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>4.447738150378264</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.1406</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>356~356</t>
-        </is>
+      <c r="B28" t="n">
+        <v>356</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>5.090831342711375</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.1556</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>284~284</t>
-        </is>
+      <c r="B29" t="n">
+        <v>284</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>3.844589848804112</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.1705</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>233~233</t>
-        </is>
+      <c r="B30" t="n">
+        <v>233</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>2.442183997386593</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.1855</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>199~199</t>
-        </is>
+      <c r="B31" t="n">
+        <v>199</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>1.275405900895549</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.2005</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>151~151</t>
-        </is>
+      <c r="B32" t="n">
+        <v>151</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-2.162312492395401</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.2155</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>127~127</t>
-        </is>
+      <c r="B33" t="n">
+        <v>127</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-3.674540682414701</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.2305</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>105~105</t>
-        </is>
+      <c r="B34" t="n">
+        <v>105</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-5.826771653543311</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.2454</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.189</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>10.60179977502812</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.174</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>103~103</t>
-        </is>
+      <c r="B7" t="n">
+        <v>103</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>6.729862650663804</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.159</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>119~119</t>
-        </is>
+      <c r="B8" t="n">
+        <v>119</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>5.489754957100956</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.144</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>152~152</t>
-        </is>
+      <c r="B9" t="n">
+        <v>152</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>6.059193258737395</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.129</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>214~214</t>
-        </is>
+      <c r="B10" t="n">
+        <v>214</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>4.983197193808721</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.1141</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>284~284</t>
-        </is>
+      <c r="B11" t="n">
+        <v>284</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>5.605153229085801</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.09909</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>364~364</t>
-        </is>
+      <c r="B12" t="n">
+        <v>364</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>4.924144097372441</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.08411</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>450~450</t>
-        </is>
+      <c r="B13" t="n">
+        <v>450</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>2.617672790901139</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.06913</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>574~574</t>
-        </is>
+      <c r="B14" t="n">
+        <v>574</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.9908822372813191</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.05415</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>741~741</t>
-        </is>
+      <c r="B15" t="n">
+        <v>741</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.131764905904987</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.03917</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>968~969</t>
-        </is>
+      <c r="B16" t="n">
+        <v>968</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.6541364991914662</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.02419</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1237~1240</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1237</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.571077808822281</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.009211</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1614~1618</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1614</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.3495777490112886</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.005769</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2051~2058</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2051</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.1610768041749893</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.02075</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2455~2462</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2455</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.7062734136299582</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.03573</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2780~2787</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2780</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.7890967342752759</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.05071</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3054~3065</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3054</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.3564073251039375</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.06569</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3249~3262</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3249</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.7153880443056195</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.08066</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3414~3427</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3414</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.640505726104351</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.09564</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3567~3580</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3567</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.5381310576401503</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.1106</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3657~3670</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3657</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.6678252411909043</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.1256</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3746~3759</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3746</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.5115282377412314</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.1406</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3815~3828</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3815</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.4819440673364142</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.1556</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3887~3900</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3887</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.2883101150817708</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.1705</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3938~3951</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3938</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.1522588719690248</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.1855</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3972~3985</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3972</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.07185739172817307</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.2005</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4020~4033</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4020</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.07288947547561975</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.2155</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4044~4057</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4044</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.1070053573843026</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.2305</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4066~4079</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4066</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.142011544953057</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.2454</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4087~4100</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4087</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.04314704564368554</v>

--- a/workspaces/btc_daily_14days/roc/roc_7.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_7.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC-7 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC-7 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>19</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-10.35580089526676</v>
+        <v>-10.34332712655906</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.025914812532065</v>
+        <v>9.038792510384809</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.384884826407756</v>
+        <v>3.397858754114857</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.766146775547575</v>
+        <v>8.77909895401541</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.231201465656049</v>
+        <v>8.244287369904178</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.975301957696637</v>
+        <v>-1.96228609834619</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.314384823328048</v>
+        <v>-7.301344569937356</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.527354302058711</v>
+        <v>-2.514193979498103</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.667971485997377</v>
+        <v>2.681154452545286</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.438736190710458</v>
+        <v>-3.425345327641928</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>12.13368800391666</v>
+        <v>12.14713736701019</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.1709917923768</v>
+        <v>12.18443882345162</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.75386887504725</v>
+        <v>11.76742223658725</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>17.26965810889358</v>
+        <v>17.25922847319303</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>16</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.486032928832174</v>
+        <v>-2.473553436896303</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-10.32490540237625</v>
+        <v>-10.3120420214787</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-10.72164303043701</v>
+        <v>-10.70867879050532</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.359545910220099</v>
+        <v>-4.346601889713163</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.897693395925273</v>
+        <v>-4.884614845537904</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-10.83934813724281</v>
+        <v>-10.82633682826219</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.68723611511782</v>
+        <v>-4.674194994672163</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.155011330628277</v>
+        <v>-5.141852152679014</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.267530978444803</v>
+        <v>7.280715214491892</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1761451676317591</v>
+        <v>0.1895367801307941</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.0284375065038347</v>
+        <v>-0.01499041281648772</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.241025159442273</v>
+        <v>-6.227580402026099</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.662663844764772</v>
+        <v>-6.649111621326355</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1645524174274442</v>
+        <v>-0.1749820531227542</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>33</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.085921545358886</v>
+        <v>8.098408974077778</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.50262391406293</v>
+        <v>9.515501322566401</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.110783544598284</v>
+        <v>9.123760643718121</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.197531204503875</v>
+        <v>3.210479433323499</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.684795428982646</v>
+        <v>5.697879437633134</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.959201992057757</v>
+        <v>2.972219671360278</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-6.199654601065788</v>
+        <v>-6.186614465128422</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-9.693598585847667</v>
+        <v>-9.68044137934065</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.703777266363161</v>
+        <v>-3.690596570906862</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.500582057962767</v>
+        <v>1.513973834092816</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.787797443030854</v>
+        <v>-7.774351913190877</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.331000804734629</v>
+        <v>1.344446398194336</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-5.147869609755816</v>
+        <v>-5.134317344053798</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.869097871968684</v>
+        <v>-1.879527507668215</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>62</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.336817214129368</v>
+        <v>2.349299213889424</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.946934892527892</v>
+        <v>3.959807455541757</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9.987494790470308</v>
+        <v>10.00047194025203</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>11.72903889943739</v>
+        <v>11.74199187376848</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.148701869020762</v>
+        <v>3.161783861913513</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.382114964856804</v>
+        <v>-1.369100066637309</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.753301089654649</v>
+        <v>1.766344082461927</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.3232973199797513</v>
+        <v>-0.3101371867088005</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.995170979368744</v>
+        <v>-1.981990199502462</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.233738455947616</v>
+        <v>-1.220347688344049</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.050293016396715</v>
+        <v>-3.036846896815405</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.404682097207491</v>
+        <v>-1.391237009061818</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.437616809622348</v>
+        <v>-3.424064533062477</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-8.02745564323105</v>
+        <v>-8.037885278929203</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>70</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7.480617095407148</v>
+        <v>7.493102215437531</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.669011811430494</v>
+        <v>-2.65614563676035</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2150238332549961</v>
+        <v>-0.2020548531834194</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.189800043305233</v>
+        <v>4.202747420146046</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.228908868444123</v>
+        <v>2.241989406601107</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.229530497756414</v>
+        <v>8.242549501518425</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8.14721550098561</v>
+        <v>8.160260687637781</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.403686130374886</v>
+        <v>3.416847028877157</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.4901977290002861</v>
+        <v>0.5033786989387892</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.213227461277654</v>
+        <v>-3.199837714575004</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.846063854764949</v>
+        <v>-4.832618490560876</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-7.668718828223668</v>
+        <v>-7.655274818445434</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-8.090768701545059</v>
+        <v>-8.077216868185346</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.557409560282402</v>
+        <v>-3.567839195979253</v>
       </c>
     </row>
     <row r="11">
@@ -835,462 +835,462 @@
         <v>80</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.49661403581058</v>
+        <v>2.509093510097991</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.092802626982966</v>
+        <v>-4.079939417194339</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.488424280503644</v>
+        <v>-4.475460023275069</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.853094566223767</v>
+        <v>-6.840155910910774</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.897333813862872</v>
+        <v>-4.884258817857535</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-9.590834821607331</v>
+        <v>-9.577826394736405</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-7.182315407587701</v>
+        <v>-7.169278287015047</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-10.14659222066172</v>
+        <v>-10.13343765850949</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-10.21005682085913</v>
+        <v>-10.19688022976075</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-13.55937048388041</v>
+        <v>-13.54598422798912</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-12.51844085651355</v>
+        <v>-12.50499758725711</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-14.98615065037197</v>
+        <v>-14.97270801555215</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-17.90953632232264</v>
+        <v>-17.89598535346794</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-21.41455241742403</v>
+        <v>-21.42498205312332</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.0916</t>
+          <t>X ≈ -0.09158</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>86</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-7.121390263355231</v>
+        <v>-7.108921569750279</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.6151012332071772</v>
+        <v>-0.6022372373621181</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.169187911872832</v>
+        <v>-2.156223861471922</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.039711333769283</v>
+        <v>-2.026771210795665</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2569168114570175</v>
+        <v>-0.2438405285041227</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.841983580178692</v>
+        <v>5.854999131970473</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.116607096669846</v>
+        <v>1.129646951161213</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.133418014711822</v>
+        <v>4.146577385104479</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.912445814316378</v>
+        <v>2.925625988915932</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.9024645081383156</v>
+        <v>0.9158539246535327</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6980920960254551</v>
+        <v>0.7115374815682003</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.591836142379137</v>
+        <v>-1.578392098930181</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.312522121853462</v>
+        <v>0.326074122908004</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.6005989290525093</v>
+        <v>-0.6110285647511944</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.07662</t>
+          <t>X ≈ -0.07661</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>124</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-4.896269077402955</v>
+        <v>-4.883801648934764</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.8767043101516663</v>
+        <v>-0.8638432460098855</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.683388701124663</v>
+        <v>-3.670428523267155</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-5.162808763015597</v>
+        <v>-5.149873387730814</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.147915543842231</v>
+        <v>3.160992179298859</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.641319049440064</v>
+        <v>2.654331237510206</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.557796366913969</v>
+        <v>2.570835494025872</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.93335408623458</v>
+        <v>-1.920198681212781</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.215998296205662</v>
+        <v>-5.202822281831246</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-8.483234086789153</v>
+        <v>-8.469848473654018</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.078632277737853</v>
+        <v>-7.065189383762949</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-11.07637546569742</v>
+        <v>-11.06293338465186</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-5.049825037686631</v>
+        <v>-5.036273687733896</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-7.221004030328196</v>
+        <v>-7.231433666025247</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.06164</t>
+          <t>X ≈ -0.06163</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.97600620619415</v>
+        <v>-3.658166221757611</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.195980883306838</v>
+        <v>-2.891869593283168</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.184024478310953</v>
+        <v>1.459898619739903</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6.688062369014126</v>
+        <v>6.932003898079266</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.763692866042248</v>
+        <v>4.022057185437824</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.509444444551853</v>
+        <v>-2.211956163784734</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.8016146992848689</v>
+        <v>-1.108712973971812</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.061094085066507</v>
+        <v>-3.357492483181801</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.7308799455457802</v>
+        <v>-1.041582842433691</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.972502333480385</v>
+        <v>-4.268848427684262</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.178381103415276</v>
+        <v>-4.474760737137409</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-4.743813240330923</v>
+        <v>-5.036721343690573</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-5.16555741574215</v>
+        <v>-5.458446471341794</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.91754642940051</v>
+        <v>-5.234505862646969</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.04666</t>
+          <t>X ≈ -0.04665</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>227</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.210409402508603</v>
+        <v>2.78406639568135</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.598239644753271</v>
+        <v>1.409350846648074</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.203869989123191</v>
+        <v>1.014961943376356</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.179214685558897</v>
+        <v>-2.368677568300647</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.9613857870323628</v>
+        <v>-1.148918717237642</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.291630697041597</v>
+        <v>3.103640118377051</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.1296121069318446</v>
+        <v>0.3829408221086936</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.219483672759686</v>
+        <v>-0.9619155240486137</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.9183341559245477</v>
+        <v>1.176209593479371</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.264646012193687</v>
+        <v>2.527958213646343</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.7386366187724107</v>
+        <v>1.003667474481126</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.3321609549711795</v>
+        <v>0.5978934729986136</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.231537568970374</v>
+        <v>1.498906305406564</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.73522731825831</v>
+        <v>2.165326316921401</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.03168</t>
+          <t>X ≈ -0.03167</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>269</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2760210652319302</v>
+        <v>0.2885433549075529</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.821493577155152</v>
+        <v>1.63424323230165</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.885834933116783</v>
+        <v>0.6986726211499175</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4662223210503811</v>
+        <v>-0.4532936007196042</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4794418160242984</v>
+        <v>0.4921464626446408</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.260505865567197</v>
+        <v>2.272617964821478</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.290420895087259</v>
+        <v>3.302315376936932</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.454821644304616</v>
+        <v>2.467274264178869</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.508304588081259</v>
+        <v>3.520417849733256</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.145902626181673</v>
+        <v>4.158119651096214</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.571065975347508</v>
+        <v>3.583589571509869</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.376690545976452</v>
+        <v>1.390022569835715</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.213049670373465</v>
+        <v>0.2268572183362636</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.693254274025215</v>
+        <v>2.682824638327062</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.0167</t>
+          <t>X ≈ -0.01669</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>377</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3769277951200323</v>
+        <v>-0.3644055054444095</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.127480741137326</v>
+        <v>0.1403905507133771</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.054249605571762</v>
+        <v>1.067256736989364</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.6563044954083423</v>
+        <v>0.6688385938512766</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3828681583508384</v>
+        <v>0.3955639338560673</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.203964249000933</v>
+        <v>3.074083210669031</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.327574003098768</v>
+        <v>2.339548782096792</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.246069547104703</v>
+        <v>4.257639690401362</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.803021512794068</v>
+        <v>1.815526681057449</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.689951310029528</v>
+        <v>0.7032180955637983</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4856408567161239</v>
+        <v>0.4991340843251635</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.01019048651780707</v>
+        <v>0.003653139503157377</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.0996519797420774</v>
+        <v>0.1135673727915858</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4463826561513926</v>
+        <v>-0.4568122918495447</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001721</t>
+          <t>X ≈ -0.001713</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>437</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.046158271799072</v>
+        <v>-2.03363598212345</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.207629489060594</v>
+        <v>-3.194719679484542</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.776373893076375</v>
+        <v>-1.763366761658773</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.07346971080962561</v>
+        <v>-0.03614523720688823</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.1142810816213782</v>
+        <v>0.003990407857436651</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2731755778828884</v>
+        <v>-0.260132681588523</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.0991216472860188</v>
+        <v>0.1117841222386105</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5456020949383458</v>
+        <v>0.5583546950331737</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7132821087956671</v>
+        <v>0.7260934495053917</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.09035711528594703</v>
+        <v>0.1039139663408619</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.256930009739897</v>
+        <v>1.270134893010905</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.8328053970029856</v>
+        <v>0.8464638531796354</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.001630140459341</v>
+        <v>0.8828781586925913</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1071867130102291</v>
+        <v>0.09675707731207694</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.01326</t>
+          <t>X ≈ 0.01327</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>404</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.470909617314959</v>
+        <v>-3.458387327639336</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.376320922661591</v>
+        <v>-1.36341111308554</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.04652024182946946</v>
+        <v>-0.03351311041186733</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.137047235752867</v>
+        <v>-2.124068093354403</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.687835917851565</v>
+        <v>-1.674725113476626</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.145862264958559</v>
+        <v>-1.132819368664194</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.216278369923565</v>
+        <v>-2.202540006486153</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.176200908794669</v>
+        <v>-3.161567773061734</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.979469560103354</v>
+        <v>-3.964192452673338</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.357529224250477</v>
+        <v>-2.342549149234941</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.563725561766866</v>
+        <v>-2.548496090572996</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.768771614003569</v>
+        <v>-3.752408642335567</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.456352957621732</v>
+        <v>-2.442796911270129</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.949205882771189</v>
+        <v>-2.959635518469341</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>325</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.406175669282995</v>
+        <v>-1.393653379607372</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.8674171868412373</v>
+        <v>-0.8545073772651861</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.105249536286266</v>
+        <v>-3.092242404868664</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.135773978322234</v>
+        <v>-1.12279483592377</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.67369636439556</v>
+        <v>-1.660585560020621</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.298858613351626</v>
+        <v>-2.285815717057261</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.461470675326822</v>
+        <v>-1.447921889651703</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.232824809134158</v>
+        <v>-2.218109134666541</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.601310912332757</v>
+        <v>-2.585935617110081</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.235266301405666</v>
+        <v>0.2492100357481561</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.12212196218568</v>
+        <v>-2.106282071906378</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.9867500920132386</v>
+        <v>1.001221085350039</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.3565814420085829</v>
+        <v>-0.34302539565698</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.354678351806172</v>
+        <v>2.344248716108019</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>4.012455325710704</v>
+        <v>3.819849275974207</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.657616347373292</v>
+        <v>1.831096916046405</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.639844556537845</v>
+        <v>-1.455714691973554</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.4148274513501562</v>
+        <v>-0.2347094423732159</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.412323839696576</v>
+        <v>-2.226764952838785</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.290682068405495</v>
+        <v>-4.097281995691063</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-5.645410878552362</v>
+        <v>-5.643959796049359</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.038169164126046</v>
+        <v>-4.838509858115714</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-5.265291656280382</v>
+        <v>-5.275225999443713</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.453031403856365</v>
+        <v>-4.835272776157183</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.57158964403326</v>
+        <v>-3.381159263245451</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.959347605909272</v>
+        <v>-2.990493704790374</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.554784698605992</v>
+        <v>-1.377990430622013</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.305063366329748</v>
+        <v>-1.515891144031848</v>
       </c>
     </row>
     <row r="22">
@@ -1404,153 +1404,153 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-6.374880083689298</v>
+        <v>-6.125126052111959</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-10.5670545078174</v>
+        <v>-10.84477165497786</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-13.00862241929013</v>
+        <v>-13.29678812023383</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-12.87378644027667</v>
+        <v>-13.16195238704319</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-10.34078399411283</v>
+        <v>-10.61299114250696</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-10.55157972281184</v>
+        <v>-10.82647044079543</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-9.111600440840292</v>
+        <v>-9.378620816290827</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-5.712039977817774</v>
+        <v>-6.253118042044704</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.752444478467353</v>
+        <v>-4.994356280207562</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-6.631421551023301</v>
+        <v>-6.363430767868181</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-7.560453578152703</v>
+        <v>-8.118676924236382</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-8.038890933627783</v>
+        <v>-8.29242252013897</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-6.920684006111145</v>
+        <v>-7.166181620875058</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.132501135373261</v>
+        <v>-4.87859030054544</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.07317</t>
+          <t>X ≈ 0.07318</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>165</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.8398950131233605</v>
+        <v>0.8524173027989832</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.258624430462127</v>
+        <v>2.271534240038179</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.984729124619243</v>
+        <v>-2.971721993201641</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.672657810193627</v>
+        <v>-4.659678667795163</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-5.211079025265796</v>
+        <v>-5.197968220890857</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.519697693610738</v>
+        <v>-5.506654797316372</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-4.392310198761805</v>
+        <v>-4.379243944461329</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-5.465554203603951</v>
+        <v>-5.452373194308713</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.314432877664927</v>
+        <v>-4.301234138710164</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.134255032389895</v>
+        <v>-2.120849904737064</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.12688714458627</v>
+        <v>-1.113429850876052</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.119617224880372</v>
+        <v>0.133069513600482</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.330940416367589</v>
+        <v>-3.317384370015986</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.081219084091266</v>
+        <v>-3.091648719789418</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.08815</t>
+          <t>X ≈ 0.08816</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>153</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.754927692861919</v>
+        <v>1.767449982537542</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.7969488511394971</v>
+        <v>0.8098586607155482</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.36286445826839</v>
+        <v>2.375871589685993</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1212614940914278</v>
+        <v>-0.1082823516929636</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.6475068333200653</v>
+        <v>0.6606176376950046</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.2913539997939338</v>
+        <v>0.3043968960882992</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.754164031203871</v>
+        <v>-1.741097776903395</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.0074107399493</v>
+        <v>3.020591749244538</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.560789938734281</v>
+        <v>5.573988677689044</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.749880439980871</v>
+        <v>2.763285567633702</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.505911429388817</v>
+        <v>4.519368723099035</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.193889357976076</v>
+        <v>5.207341646696186</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.427229518273045</v>
+        <v>5.440785564624647</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.369761308065591</v>
+        <v>4.359331672367439</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>90</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-5.826771653543247</v>
+        <v>-5.814249363867624</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-5.610991750881936</v>
+        <v>-5.597984619464334</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5.480738618274437</v>
+        <v>-5.467759475875972</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.796937611124385</v>
+        <v>-3.783826806749445</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-9.055051228964338</v>
+        <v>-9.042008332669973</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.806451612903153</v>
+        <v>-5.793385358602677</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.940301678351332</v>
+        <v>-2.927120669056094</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-5.223523786755848</v>
+        <v>-5.210325047801085</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.629204527339397</v>
+        <v>-1.615799399686566</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.7228467405459256</v>
+        <v>-0.7093894468357078</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.644869750132834</v>
+        <v>2.658322038852944</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>3.349282296650713</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.8589968618690449</v>
+        <v>-0.869426497567197</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>89</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5.933527971924789</v>
+        <v>5.946050261600412</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>15.55790941514038</v>
+        <v>15.57081922471643</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>12.91584969730783</v>
+        <v>12.92885682872544</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>11.92250732429738</v>
+        <v>11.93548646669584</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.766108581135235</v>
+        <v>5.779219385510174</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.816359507614997</v>
+        <v>3.829402403909363</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.34960331843255</v>
+        <v>9.362669572733026</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8.882419919651049</v>
+        <v>8.895600928946287</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8.821420033468748</v>
+        <v>8.834618772423511</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>12.46567687091279</v>
+        <v>12.47908199856562</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>12.26092354659521</v>
+        <v>12.27438084030543</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.924520187086642</v>
+        <v>8.937972475806752</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>9.627861081759782</v>
+        <v>9.641417128111385</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.383200391564102</v>
+        <v>5.37277075586595</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>69</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.129750085587133</v>
+        <v>1.142272375262756</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-3.380374252014775</v>
+        <v>-3.367464442438724</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.775242958611443</v>
+        <v>-3.762235827193841</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-6.543540550641666</v>
+        <v>-6.530561408243202</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-7.081961765713665</v>
+        <v>-7.068850961338725</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.436693741041573</v>
+        <v>-2.423650844747208</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.521427458313809</v>
+        <v>-2.508361204013333</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.09006013245766553</v>
+        <v>-0.07687912316242773</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.1510600186399671</v>
+        <v>-0.1378612796852039</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.450460565986731</v>
+        <v>-2.4370554383339</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.2433368343334052</v>
+        <v>0.256794128043623</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.726995353997715</v>
+        <v>1.740447642717825</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.591809981585023</v>
+        <v>-1.57825393523342</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.00573743764798</v>
+        <v>2.995307801949828</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>72</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>10.00656167979002</v>
+        <v>10.01908396946565</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.450543622381282</v>
+        <v>1.463453431957333</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>13.55567491578476</v>
+        <v>13.56868204720237</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.13037249283672</v>
+        <v>8.143351635235184</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>8.980840166653394</v>
+        <v>8.993950971028333</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.11161543770239</v>
+        <v>5.124658333996756</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.415770609318962</v>
+        <v>6.428836863619438</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>11.51732377538828</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>11.45634161886551</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>11.98190658377167</v>
+        <v>11.99531171142451</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.38826437056521</v>
+        <v>10.40172166427543</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>11.8115364167996</v>
+        <v>11.82498870551971</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>8.863225360353127</v>
+        <v>8.852795724654975</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>51</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>10.25165971900571</v>
+        <v>10.26418200868133</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>12.56165473349242</v>
+        <v>12.57456454306848</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.245217399444861</v>
+        <v>8.258224530862464</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>12.29703915950328</v>
+        <v>12.31001830190174</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>11.75861794443111</v>
+        <v>11.77172874880605</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>15.97762850959788</v>
+        <v>15.99067140589224</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>15.89289479232549</v>
+        <v>15.90596104662596</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.54335845236762</v>
+        <v>9.556539461662858</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>11.45634161886551</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.632233381157391</v>
+        <v>8.645638508810222</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.545127115663348</v>
+        <v>2.558584409373566</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.501078900459696</v>
+        <v>6.514531189179806</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.159255662063821</v>
+        <v>2.172811708415423</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.4481926806146674</v>
+        <v>0.4377630449165153</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>34</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>9.271267562142967</v>
+        <v>9.28378985181859</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.659693949178752</v>
+        <v>7.672603758754803</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.382472301405649</v>
+        <v>1.395479432823251</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.395078375189698</v>
+        <v>7.408057517588162</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>12.739010101294</v>
+        <v>12.75212090566894</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>13.03645203900949</v>
+        <v>13.04949493530385</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>10.01054185114915</v>
+        <v>10.02360810544963</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.602181981779246</v>
+        <v>6.615362991074484</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.54118209559703</v>
+        <v>6.554380834551793</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.632233381157249</v>
+        <v>8.64563850881008</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.486303586251438</v>
+        <v>5.499760879961656</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.40303968477333</v>
+        <v>11.41649197349344</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.98278507382853</v>
+        <v>10.99634112018013</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>8.291329935516487</v>
+        <v>8.280900299818335</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>48</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>12.08989501312332</v>
+        <v>12.10241730279895</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.47832140015907</v>
+        <v>10.49123120973512</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>18.41678602689583</v>
+        <v>18.42979315831344</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>16.46370582617002</v>
+        <v>16.47668496856848</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>20.09195127776451</v>
+        <v>20.10506208213945</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>26.63939321548017</v>
+        <v>26.65243611177453</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>20.30465949820789</v>
+        <v>20.31772575250837</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>13.58747609942642</v>
+        <v>13.60065710872166</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>17.69314287991075</v>
+        <v>17.70634161886551</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>14.75968436154956</v>
+        <v>14.77308948920239</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>18.72159770389855</v>
+        <v>18.73505499760877</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.50598086124398</v>
+        <v>12.51943314996409</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>16.25239291696581</v>
+        <v>16.26594896331741</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>16.50211424924206</v>
+        <v>16.4916846135439</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>24</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5.839895013123417</v>
+        <v>5.85241730279904</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.228321400159103</v>
+        <v>4.241231209735155</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>12.16678602689583</v>
+        <v>12.17979315831344</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>15.92528461109778</v>
+        <v>15.93839541547272</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12.05605988214683</v>
+        <v>12.06910277844119</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>16.13799283154116</v>
+        <v>16.15105908584164</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.50414276609295</v>
+        <v>11.51732377538818</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>15.60980954657743</v>
+        <v>15.62300828553219</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>18.9263510282161</v>
+        <v>18.93975615586893</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>22.88826437056524</v>
+        <v>22.90172166427546</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>27.08931419457736</v>
+        <v>27.10276648329747</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>22.50239291696571</v>
+        <v>22.51594896331731</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>22.752114249242</v>
+        <v>22.74168461354385</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>22</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.597470770699118</v>
+        <v>6.609993060374741</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>9.531351703189401</v>
+        <v>9.544261512765452</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.591028451138307</v>
+        <v>4.604035582555909</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>22.90309976556394</v>
+        <v>22.91607890796241</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>13.27376945958275</v>
+        <v>13.28688026395769</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>18.1166659427529</v>
+        <v>18.12970883904727</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>18.03193222548068</v>
+        <v>18.04499847978116</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>17.56474882669918</v>
+        <v>17.57792983599442</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>17.50374894051682</v>
+        <v>17.51694767947158</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>16.65362375548895</v>
+        <v>16.66702888314178</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>25.53977952208047</v>
+        <v>25.55323681579068</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>16.48325358851686</v>
+        <v>16.49670587723697</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>16.06299897757184</v>
+        <v>16.07655502392345</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>20.85817485530281</v>
+        <v>20.84774521960465</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>21</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-19.16010498687665</v>
+        <v>-19.14758269720102</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>22.08546425730196</v>
+        <v>22.09837406687801</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.404881264991054</v>
+        <v>7.417888396408657</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>17.05894392140811</v>
+        <v>17.07192306380657</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>11.75861794443117</v>
+        <v>11.7717287488061</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>16.8179646440516</v>
+        <v>16.83100754034596</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>16.73323092677932</v>
+        <v>16.7462971810798</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>16.26604752799782</v>
+        <v>16.27922853729306</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6.681238118005993</v>
+        <v>6.694436856960756</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>15.35492245678759</v>
+        <v>15.36832758444042</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>5.626359608660486</v>
+        <v>5.639816902370704</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.660742766005853</v>
+        <v>5.674195054725963</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.76429767887054</v>
+        <v>14.77785372522214</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.01401901114673</v>
+        <v>15.00358937544858</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC-7 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC-7 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,53 +2210,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.189</t>
+          <t>X &gt; -0.1889</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4087</v>
+        <v>4088</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2251456372831413</v>
+        <v>-0.2253686030776336</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1162341825033408</v>
+        <v>-0.1164923675006193</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3027112888679468</v>
+        <v>-0.3029262041326817</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2324539655475064</v>
+        <v>-0.2326854560288893</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1961346597354918</v>
+        <v>-0.1963779959664791</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.08069225460530305</v>
+        <v>-0.08096232572546569</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.02997655455224191</v>
+        <v>-0.0302595954769842</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.09289282312430913</v>
+        <v>-0.09316311599746996</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.03063066094691891</v>
+        <v>0.03032972864644989</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.04822731448733464</v>
+        <v>-0.04851363885241966</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.01923359194493912</v>
+        <v>-0.01952823387494362</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1178269157185667</v>
+        <v>-0.1180974123830651</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.08403891604139346</v>
+        <v>-0.08432005111157537</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.06515187913245057</v>
+        <v>-0.06490377523626023</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4068</v>
+        <v>4069</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1778294008274699</v>
+        <v>-0.1781232818817244</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.158933501801684</v>
+        <v>-0.159242530361233</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.319934574558765</v>
+        <v>-0.3202068416865558</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2744828283992291</v>
+        <v>-0.2747655503495636</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2354953741854544</v>
+        <v>-0.2357912773504935</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.07184329089862729</v>
+        <v>-0.07217757475967801</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.004046001275369804</v>
+        <v>0.003692386463221453</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.08152242781955721</v>
+        <v>-0.0818582287016909</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.01831269740809915</v>
+        <v>0.01795182996026767</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.03239160439680688</v>
+        <v>-0.0327456855255619</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.07599502516061563</v>
+        <v>-0.07633989433618638</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1752230699599195</v>
+        <v>-0.1755435142461437</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1393290458424516</v>
+        <v>-0.1396611922927775</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1461158392535111</v>
+        <v>-0.1457979784115224</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4052</v>
+        <v>4053</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.1687150729774984</v>
+        <v>-0.1690616281733028</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1187914607332843</v>
+        <v>-0.1191623942008846</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.278861688257166</v>
+        <v>-0.279196342998894</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2583522732883878</v>
+        <v>-0.2586911902632565</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2170859051953613</v>
+        <v>-0.2174391487812812</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.02932599634248589</v>
+        <v>-0.02972345483467365</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.02257031367968665</v>
+        <v>0.02215925004530561</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.06148890796640671</v>
+        <v>-0.0618829257696305</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.01031205394842516</v>
+        <v>-0.010719330699132</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.0332150467345329</v>
+        <v>-0.03362318847411672</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.07618281398058002</v>
+        <v>-0.07658208325904781</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1512712354506149</v>
+        <v>-0.1516519301838457</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.1135705668733564</v>
+        <v>-0.1139638799649774</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1460430393397019</v>
+        <v>-0.1456827686421249</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4019</v>
+        <v>4020</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2364938757655324</v>
+        <v>-0.2369289241619299</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1977928808298941</v>
+        <v>-0.198252917248972</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.355960044237321</v>
+        <v>-0.3563847958749236</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2867285247855662</v>
+        <v>-0.2871694565762724</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2655462396138475</v>
+        <v>-0.2659977341921476</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.05386479296284108</v>
+        <v>-0.05436627154224993</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.07366098852084946</v>
+        <v>0.07312679546838297</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01760032302887993</v>
+        <v>0.01707538989401058</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.02001498063971496</v>
+        <v>0.01948861679512248</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.04580905132647217</v>
+        <v>-0.04632734313697995</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.01286276353055626</v>
+        <v>-0.01339143540138821</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1634421678532263</v>
+        <v>-0.1639333343720324</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.07223394870587185</v>
+        <v>-0.07275202317022433</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1318950399675245</v>
+        <v>-0.1314497148142948</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3957</v>
+        <v>3958</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2768136350714414</v>
+        <v>-0.2774408353694042</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2627342813727722</v>
+        <v>-0.2633867583588838</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.5180258010611496</v>
+        <v>-0.5186195400992517</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4749968038610746</v>
+        <v>-0.4755999776680824</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3190421665118421</v>
+        <v>-0.3196921401948174</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.03305319057279377</v>
+        <v>-0.03377165423655981</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.04734365562464404</v>
+        <v>0.04660343220572116</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.02294165582306107</v>
+        <v>0.02220100377712697</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.05158979224459159</v>
+        <v>0.05084073569619818</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.02719605585351559</v>
+        <v>-0.02793692843187046</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.03472901702989617</v>
+        <v>0.03396941316042756</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1439938798522249</v>
+        <v>-0.1447082641772965</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.01950366379891477</v>
+        <v>-0.02025546541041479</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.008183956469331122</v>
+        <v>-0.007599536700318765</v>
       </c>
     </row>
     <row r="11">
@@ -2474,517 +2474,517 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3887</v>
+        <v>3888</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4165152432869021</v>
+        <v>-0.4173425878273491</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2194002378677453</v>
+        <v>-0.2203072518033053</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.5234824868719059</v>
+        <v>-0.5243190071990753</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5590039505813422</v>
+        <v>-0.5598294832871744</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.3649275723381606</v>
+        <v>-0.3658129499365046</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1818519706558988</v>
+        <v>-0.1827794939749481</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.09852488802734172</v>
+        <v>-0.09947578792809253</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.03794131644826138</v>
+        <v>-0.03891659441139694</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.04369101283299415</v>
+        <v>0.04269319006167649</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.03018037799770212</v>
+        <v>0.02917033880835618</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1226259815335382</v>
+        <v>0.1215880225381198</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.008483011216775083</v>
+        <v>-0.009487158519171146</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1258497070892304</v>
+        <v>0.1248029960593016</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.05573314985093702</v>
+        <v>0.05649942835871968</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.09909</t>
+          <t>X &gt; -0.09907</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3807</v>
+        <v>3808</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.4777315139272531</v>
+        <v>-0.4788223377837681</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1380048632606474</v>
+        <v>-0.1392225424463476</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.4401635103837123</v>
+        <v>-0.4413118429957947</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4267404230658656</v>
+        <v>-0.4278898524547401</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2696839423612758</v>
+        <v>-0.2708876165768217</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.01586765846837324</v>
+        <v>0.01459544091499509</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.05033333145382102</v>
+        <v>0.04904947465777099</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1744810823794438</v>
+        <v>0.1731531758427565</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2591624671790314</v>
+        <v>0.2578102787134071</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.3157501360618653</v>
+        <v>0.3143626616402457</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3882643705652455</v>
+        <v>0.3868524261052499</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3062565241476634</v>
+        <v>0.3048662208302559</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.5048438973579294</v>
+        <v>0.5033909865955835</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.5069080501351593</v>
+        <v>0.5077910561209436</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.08411</t>
+          <t>X &gt; -0.08409</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3721</v>
+        <v>3722</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3241828301189145</v>
+        <v>-0.3256282125959302</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1269781801605703</v>
+        <v>-0.1285241910861288</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4002021831791822</v>
+        <v>-0.4016873310159568</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3894613318751965</v>
+        <v>-0.3909463283232739</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.269979017141651</v>
+        <v>-0.2715125627278852</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1187859210175475</v>
+        <v>-0.1203520919788161</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.02568954112634003</v>
+        <v>0.02408134381970228</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.08298186814117514</v>
+        <v>0.08134380400060337</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.1978396056219722</v>
+        <v>0.196168110234801</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3021899543906557</v>
+        <v>0.3004646904905641</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3811036115247859</v>
+        <v>0.3793502996222244</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3501253683619296</v>
+        <v>0.34838051838517</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5092888510513944</v>
+        <v>0.5074880447033649</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.5325048252520972</v>
+        <v>0.5336423423635495</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.06913</t>
+          <t>X &gt; -0.06912</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3597</v>
+        <v>3598</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1665685141157951</v>
+        <v>-0.1685371881084308</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.101132742262628</v>
+        <v>-0.1031824560081489</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2870203293495379</v>
+        <v>-0.2890347718611181</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2249089044463872</v>
+        <v>-0.2269366131018913</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3878046845205745</v>
+        <v>-0.3898090018638811</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2139354946446588</v>
+        <v>-0.2159776430784888</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.06160021322385489</v>
+        <v>-0.06368894929467928</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1524913644832893</v>
+        <v>0.1503241453475894</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.3844717712674068</v>
+        <v>0.3822367062926588</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.6050513892269862</v>
+        <v>0.6027211753026478</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.6382643705652526</v>
+        <v>0.635915869588807</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.744033097976434</v>
+        <v>0.7416553721863437</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.700929140793825</v>
+        <v>0.6985459810074772</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.7997928703151871</v>
+        <v>0.8012547450984755</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.05415</t>
+          <t>X &gt; -0.05414</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>3430</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.0189055659358317</v>
+        <v>0.002383417621324213</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.04954936839462931</v>
+        <v>0.03340630173592984</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3586426275650751</v>
+        <v>-0.3746968155313652</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5614879722796005</v>
+        <v>-0.5775785973230043</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5899329909182498</v>
+        <v>-0.6059004069562164</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1021716478124404</v>
+        <v>-0.1182154298194149</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.0255703534068914</v>
+        <v>-0.01250409910641537</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.3089545627558365</v>
+        <v>0.3221355720510743</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.4387760676836763</v>
+        <v>0.4519748066384395</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8279235384083634</v>
+        <v>0.8413286660611945</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8727774300855913</v>
+        <v>0.886234723795809</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.011225616488773</v>
+        <v>1.024677905208883</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.9865569119138016</v>
+        <v>1.000112958265404</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.078158952837796</v>
+        <v>1.096883836090079</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.03917</t>
+          <t>X &gt; -0.03916</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3203</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.2072796887947419</v>
+        <v>-0.1947573991191192</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.06020795059800577</v>
+        <v>-0.06410834443799018</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4693795504461988</v>
+        <v>-0.4731834025660362</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4468379679354229</v>
+        <v>-0.4506415175815377</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5636077381183995</v>
+        <v>-0.5674161245853426</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3426940119341637</v>
+        <v>-0.3465517424764784</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.03656829861354538</v>
+        <v>-0.04052969920502392</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4172765981795052</v>
+        <v>0.4131376322492102</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4047892784140288</v>
+        <v>0.4006475207774045</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.7261014960888943</v>
+        <v>0.7217954449241901</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.8822841313556751</v>
+        <v>0.8779121404659378</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.059351647760863</v>
+        <v>1.054924569620908</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.9691948734648932</v>
+        <v>0.9647629458392259</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.031591822350606</v>
+        <v>1.021162186652454</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.02419</t>
+          <t>X &gt; -0.02418</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2934</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.2515904941230218</v>
+        <v>-0.2390682044473991</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.2327293244785764</v>
+        <v>-0.2198195149025253</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.5936306397708222</v>
+        <v>-0.5806235083532201</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.4450607385598531</v>
+        <v>-0.4503983647648582</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.6592383891287596</v>
+        <v>-0.6645607517035685</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5813650300145525</v>
+        <v>-0.586686933772711</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.3415990051934727</v>
+        <v>-0.3470141318847055</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.2304669126281595</v>
+        <v>0.224806768585573</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1202474862189078</v>
+        <v>0.1146154081362525</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.4125614470108516</v>
+        <v>0.406740498959536</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6357666412282796</v>
+        <v>0.6298456002645736</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.03025684080108</v>
+        <v>1.024201542334694</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.038521069658351</v>
+        <v>1.032416879274223</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.8792444469244103</v>
+        <v>0.8688148112262581</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.009211</t>
+          <t>X &gt; -0.009202</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2557</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2331109624547096</v>
+        <v>-0.2205886727790869</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2858381217946473</v>
+        <v>-0.2729283122185961</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.8365914737536713</v>
+        <v>-0.8235843423360691</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6074442712958756</v>
+        <v>-0.6154168760664973</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.8128849156832345</v>
+        <v>-0.8208638437864764</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.139467938966007</v>
+        <v>-1.126425042671642</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.7351376145505952</v>
+        <v>-0.7431166811889796</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.3615871324237219</v>
+        <v>-0.3697876825386146</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1278580311916713</v>
+        <v>-0.1361642359354249</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3716635282161604</v>
+        <v>0.3630283151817579</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.6579009473530562</v>
+        <v>0.6491174976087919</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.183658734582558</v>
+        <v>1.174669570440869</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.176946430197432</v>
+        <v>1.167890584375499</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.074692791804964</v>
+        <v>1.064263156106811</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.005769</t>
+          <t>X &gt; 0.005777</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2120</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1406162423488198</v>
+        <v>0.1531385320244425</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3164367968351698</v>
+        <v>0.3293466064112209</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6428721731668716</v>
+        <v>-0.6298650417492695</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.7478024836449819</v>
+        <v>-0.7348233412465177</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.004003567014422</v>
+        <v>-0.9908927626394828</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.318038581321332</v>
+        <v>-1.304995685026967</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.9071052076744621</v>
+        <v>-0.9193391581219217</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.5485879307054304</v>
+        <v>-0.5611075971607207</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.301243994009802</v>
+        <v>-0.3139032022267685</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.4296498029569662</v>
+        <v>0.4164400936928274</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.534421843455398</v>
+        <v>0.5211058929905121</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.255980861244005</v>
+        <v>1.242323296121597</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.213084740865142</v>
+        <v>1.226640787216745</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.27412682785841</v>
+        <v>1.263697192160258</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.02075</t>
+          <t>X &gt; 0.02076</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1716</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.9908822372813191</v>
+        <v>1.003404526956942</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7149648380220555</v>
+        <v>0.7278746475981066</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.7832720451134421</v>
+        <v>-0.7702649136958399</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.4207308753398635</v>
+        <v>-0.4077517329413993</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.8430080718289901</v>
+        <v>-0.8298972674540508</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.35857426419463</v>
+        <v>-1.345531367900264</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.5988849526927424</v>
+        <v>-0.6172335970851321</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.07003423896127003</v>
+        <v>0.05112195474138304</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.5647251952103503</v>
+        <v>0.545488905687229</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.085838804700444</v>
+        <v>1.065992339696798</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.263822514614951</v>
+        <v>1.24378608026305</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.438964544227694</v>
+        <v>2.418239207040422</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.07698499155785</v>
+        <v>2.090541037909453</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.26843126555908</v>
+        <v>2.258001629860928</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>1391</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.55094249582438</v>
+        <v>1.563464785500003</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.084680264391977</v>
+        <v>1.097590073968028</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.2407539396992391</v>
+        <v>-0.227746808281637</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2536647297832246</v>
+        <v>-0.2406855873847604</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6489220221639087</v>
+        <v>-0.6358112177889694</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.138881659251396</v>
+        <v>-1.125838762957031</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3973462324511345</v>
+        <v>-0.4231475474200508</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.6080854184228031</v>
+        <v>0.5813161345095921</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.304453257720418</v>
+        <v>1.27713014933147</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.284570697993615</v>
+        <v>1.256829326600695</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.054931037231917</v>
+        <v>2.026512284040955</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.778266986333875</v>
+        <v>2.74931820743538</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.645575279774306</v>
+        <v>2.659131326125909</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.248280077183594</v>
+        <v>2.237850441485442</v>
       </c>
     </row>
     <row r="22">
@@ -3046,49 +3046,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.9471336190214785</v>
+        <v>1.007456062488899</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.9441390945290706</v>
+        <v>0.9168424202300827</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1024428633569698</v>
+        <v>0.07484384406181022</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2141315286110412</v>
+        <v>-0.2421582037630614</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.2163597141925919</v>
+        <v>-0.2437751271628841</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3657453010524563</v>
+        <v>-0.3936282889410307</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.8900035554018118</v>
+        <v>0.8633429260325158</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.993111162038197</v>
+        <v>1.916846733050782</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.916011096965022</v>
+        <v>2.891734039038603</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.692003979915626</v>
+        <v>2.758019360882422</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.435116056629113</v>
+        <v>3.359047835567615</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.185703332148222</v>
+        <v>4.163698382939032</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.675923206431605</v>
+        <v>3.653941794858596</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.119914905762514</v>
+        <v>3.162831566948931</v>
       </c>
     </row>
     <row r="23">
@@ -3101,150 +3101,150 @@
         <v>922</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.495715692805206</v>
+        <v>2.508237982480829</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.378719086348546</v>
+        <v>3.391628895924597</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.875390509903802</v>
+        <v>2.888397641321404</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.463344293270517</v>
+        <v>2.476323435668981</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.924923078198347</v>
+        <v>1.938033882573286</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.788525536521384</v>
+        <v>1.801568432815749</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.005310257426977</v>
+        <v>3.018376511727453</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.62272555712704</v>
+        <v>3.635906566422278</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.537864499578149</v>
+        <v>4.551063238532912</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.663878143183624</v>
+        <v>4.677283270836455</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.760643257043917</v>
+        <v>5.774100550754135</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.771165243022757</v>
+        <v>6.784617531742867</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.917071152685224</v>
+        <v>5.930627199036827</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4.86527404678364</v>
+        <v>4.854844411085487</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.08066</t>
+          <t>X &gt; 0.08067</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>757</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.856627729988176</v>
+        <v>2.869150019663799</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.622861250445318</v>
+        <v>3.635771060021369</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.152695317957047</v>
+        <v>4.165702449374649</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.018747657962173</v>
+        <v>4.031726800360637</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.480326442890004</v>
+        <v>3.493437247264943</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.381467191702093</v>
+        <v>3.394510087996458</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.617737437441704</v>
+        <v>4.63080369174218</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.603658397973291</v>
+        <v>5.616839407268529</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.467361285899308</v>
+        <v>6.480560024854071</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.145637686076135</v>
+        <v>6.159042813728966</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>7.261888324770446</v>
+        <v>7.275345618480664</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>8.220974256224196</v>
+        <v>8.234426544944306</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.932820041580491</v>
+        <v>7.946376087932094</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.597336618242508</v>
+        <v>6.586906982544356</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.09564</t>
+          <t>X &gt; 0.09565</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>604</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.135700752637703</v>
+        <v>3.148223042313326</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.338696676097292</v>
+        <v>4.351606485673344</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.606079625129837</v>
+        <v>4.619086756547439</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.067458585551911</v>
+        <v>5.080437727950375</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.197911542665167</v>
+        <v>4.211022347040107</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.164227652566254</v>
+        <v>4.177270548860619</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>6.231811816088687</v>
+        <v>6.244878070389163</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>6.261317159029034</v>
+        <v>6.274498168324271</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>6.697006014568593</v>
+        <v>6.710204753523357</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.005821226891655</v>
+        <v>7.019226354544486</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.960008299925065</v>
+        <v>7.973465593635282</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8.987768940714204</v>
+        <v>9.001221229434314</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8.567514329769303</v>
+        <v>8.581070376120906</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.161606522972754</v>
+        <v>7.151176887274602</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>514</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.705005259556557</v>
+        <v>4.71752754923218</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.817167055152616</v>
+        <v>5.830076864728667</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.39506099447042</v>
+        <v>6.408068125888022</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.914419185443684</v>
+        <v>6.927398327842148</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.597787853639993</v>
+        <v>5.610898658014932</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.478887378904297</v>
+        <v>6.491930275198662</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8.339678953460805</v>
+        <v>8.352745207761281</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>7.872495554679304</v>
+        <v>7.885676563974542</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8.784258314411396</v>
+        <v>8.797457053366159</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.517790716932112</v>
+        <v>8.531195844584943</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.480352567711805</v>
+        <v>9.493809861422022</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>10.09839331260588</v>
+        <v>10.11184560132599</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>9.483586172478091</v>
+        <v>9.497142218829694</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.565992329657107</v>
+        <v>8.555562693958954</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>425</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.447738150378264</v>
+        <v>4.460260440053887</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.777341008002239</v>
+        <v>3.79025081757829</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.029531124935062</v>
+        <v>5.042538256352664</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.865666610483729</v>
+        <v>5.878645752882193</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.562539513058631</v>
+        <v>5.575650317433571</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.036452039009582</v>
+        <v>7.049494935303947</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.1281889099726</v>
+        <v>8.141255164273076</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.6610055111911</v>
+        <v>7.674186520486337</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.776476213244088</v>
+        <v>8.789674952198851</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>7.691056910569102</v>
+        <v>7.704462038221934</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.898068292133871</v>
+        <v>8.911525585844089</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>10.34421615536166</v>
+        <v>10.35766844408177</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>9.453373309122632</v>
+        <v>9.466929355474235</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>9.232506406104818</v>
+        <v>9.222076770406666</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>356</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.090831342711375</v>
+        <v>5.103353632386998</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.164650988174074</v>
+        <v>5.177560797750125</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.736074416408961</v>
+        <v>6.749081547826563</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.270821931038931</v>
+        <v>8.283801073437395</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>8.013299592371247</v>
+        <v>8.026410396746186</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>8.8725392828959</v>
+        <v>8.885582179190266</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10.19229994764608</v>
+        <v>10.20536620194656</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>9.163318796055599</v>
+        <v>9.176499805350836</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>10.50681329189577</v>
+        <v>10.52001203085054</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.656688106867847</v>
+        <v>9.670093234520678</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.57553028816824</v>
+        <v>10.58898758187846</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>12.01440782753615</v>
+        <v>12.02786011625626</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.59415321659124</v>
+        <v>11.60770926294285</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>10.43938016684505</v>
+        <v>10.4289505311469</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>284</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.844589848804112</v>
+        <v>3.857112138479735</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.106255672459568</v>
+        <v>6.119165482035619</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.007161613750306</v>
+        <v>5.020168745167908</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.306428830864853</v>
+        <v>8.319407973263317</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.768007615792683</v>
+        <v>7.781118420167623</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>9.826012933790025</v>
+        <v>9.839055830084391</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>11.14972992074311</v>
+        <v>11.16279617504358</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.569870465623573</v>
+        <v>8.583051474918811</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>10.26943395972297</v>
+        <v>10.28263269867773</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.067196098638703</v>
+        <v>9.080601226291535</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.62300615460281</v>
+        <v>10.63646344831302</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>12.06584001617358</v>
+        <v>12.07929230489369</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>11.99769808128503</v>
+        <v>12.01125412763663</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.83896870933596</v>
+        <v>10.82853907363781</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>233</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.442183997386593</v>
+        <v>2.454706287062216</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.693271328628342</v>
+        <v>4.706181138204393</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.298402622031752</v>
+        <v>4.311409753449354</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.43294760013282</v>
+        <v>7.445926742531285</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>6.894526385060651</v>
+        <v>6.90763718943559</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>8.479521970844971</v>
+        <v>8.492564867139336</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>10.11152645099759</v>
+        <v>10.12459270529807</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>8.356789404147413</v>
+        <v>8.369970413442651</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>10.01252771539001</v>
+        <v>10.02572645434478</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.162402530362087</v>
+        <v>9.175807658014918</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>12.39112560089428</v>
+        <v>12.4045828946045</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>13.28387785695216</v>
+        <v>13.29733014567227</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>14.15117689407594</v>
+        <v>14.16473294042754</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>13.11334457828355</v>
+        <v>13.10291494258539</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>199</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.275405900895549</v>
+        <v>1.287928190571172</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.186445353257923</v>
+        <v>4.199355162833974</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.796601772289478</v>
+        <v>4.80960890370708</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.439417718967334</v>
+        <v>7.452396861365798</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.895971378267021</v>
+        <v>5.90908218264196</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>7.700951004424894</v>
+        <v>7.713993900719259</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>10.12878010122297</v>
+        <v>10.14184635552344</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>8.65657157681332</v>
+        <v>8.669752586108558</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>10.6056219418873</v>
+        <v>10.61882068084206</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.252984194045311</v>
+        <v>9.266389321698142</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.57084393505436</v>
+        <v>13.58430122876457</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>13.60522709239979</v>
+        <v>13.6186793811199</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>14.6925101698971</v>
+        <v>14.7060662162487</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>13.93720637654525</v>
+        <v>13.9267767408471</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>151</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.162312492395401</v>
+        <v>-2.149790202719778</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.186378795302588</v>
+        <v>2.199288604878639</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.4670067774477218</v>
+        <v>0.4800139088653239</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.570769843830057</v>
+        <v>4.583748986228521</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.383342006241328</v>
+        <v>1.396452810616267</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.680783943956989</v>
+        <v>1.693826840251354</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.894063471717828</v>
+        <v>6.907129726018304</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>7.089131728565455</v>
+        <v>7.102312737860693</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.352635153641444</v>
+        <v>8.365833892596207</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>7.502509968613516</v>
+        <v>7.515915096266347</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>11.93351823369991</v>
+        <v>11.94697552741013</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>13.95465635793276</v>
+        <v>13.96810864665287</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>14.19665340261698</v>
+        <v>14.21020944896858</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>13.121871423635</v>
+        <v>13.11144178793685</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>127</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-3.674540682414701</v>
+        <v>-3.662018392739078</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.80049987784939</v>
+        <v>1.813409687425441</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.7439751279598</v>
+        <v>-1.730967996542198</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.110687453466596</v>
+        <v>3.12366659586506</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.364741635621314</v>
+        <v>-1.351630831246375</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2798981231025053</v>
+        <v>-0.2668552268081399</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.147179183247268</v>
+        <v>5.160245437547744</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.254798934072063</v>
+        <v>6.267979943367301</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.98120062269291</v>
+        <v>6.994399361647673</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.343673862861834</v>
+        <v>5.357078990514665</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>9.863329987363159</v>
+        <v>9.876787281073376</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>11.47251629431489</v>
+        <v>11.485968583035</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.62706483297628</v>
+        <v>12.64062087932788</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>11.30198301564627</v>
+        <v>11.29155337994812</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>105</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-5.826771653543311</v>
+        <v>-5.814249363867688</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1807023525400524</v>
+        <v>0.1936121621161035</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-3.071309211199399</v>
+        <v>-3.058302079781797</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.036294173829987</v>
+        <v>-1.023315031431522</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-4.431858246045017</v>
+        <v>-4.418747441670078</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-4.134416308329357</v>
+        <v>-4.121373412034991</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.447516641065029</v>
+        <v>2.460582895365505</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>3.88509514704544</v>
+        <v>3.898276156340678</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>4.789674952198851</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.973970075835211</v>
+        <v>2.987375203488043</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.578740561041435</v>
+        <v>6.592197854751653</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.90715482172768</v>
+        <v>11.92071086807928</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>9.299733296861106</v>
+        <v>9.289303661162954</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-5.295488123650422</v>
+        <v>-5.282578314074371</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-5.690356830247012</v>
+        <v>-5.67734969882941</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-5.560103697639512</v>
+        <v>-5.547124555241048</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-8.479477293664061</v>
+        <v>-8.466366489289122</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-9.37251154642459</v>
+        <v>-9.359468650130225</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.123911930363541</v>
+        <v>-1.110845676063065</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.7898570518073456</v>
+        <v>0.8030380611025834</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.300285737053613</v>
+        <v>4.313484476008377</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1212680194028835</v>
+        <v>-0.1078628917500524</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>6.816835799136676</v>
+        <v>6.830293092846894</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>11.61312371838687</v>
+        <v>11.62657600710698</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>11.19286910744197</v>
+        <v>11.20642515379357</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>7.87116186828969</v>
+        <v>7.860732232591538</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC-7 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC-7 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,53 +3904,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.189</t>
+          <t>X &lt; -0.1889</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.60179977502812</v>
+        <v>10.61432206470374</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.799749971587673</v>
+        <v>7.812659781163724</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.54773840784823</v>
+        <v>14.56074553926583</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.3100183019018</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.56814175395499</v>
+        <v>10.58125255832993</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.103678929765877</v>
+        <v>6.116721826060243</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.828469022017416</v>
+        <v>4.841535276317892</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>7.932714194664484</v>
+        <v>7.945895203959722</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.109809546577424</v>
+        <v>3.123008285532187</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.021589123454255</v>
+        <v>7.034994251107086</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.626359608660486</v>
+        <v>5.639816902370704</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.811916726489592</v>
+        <v>8.825472772841195</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.87116186828969</v>
+        <v>7.860732232591538</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>103</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6.729862650663804</v>
+        <v>6.742384940339427</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.030910396922849</v>
+        <v>8.0438202064989</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>12.4904106223651</v>
+        <v>12.50341775378271</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>11.64978996856484</v>
+        <v>11.6627691109633</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10.1404949670849</v>
+        <v>10.15360577145984</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.612694186353949</v>
+        <v>4.625737082648314</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.58621289626614</v>
+        <v>2.599279150566616</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.002524643115706</v>
+        <v>6.015705652410944</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.028903397710103</v>
+        <v>3.042102136664866</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.091399571905477</v>
+        <v>5.104804699558308</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.828393820403441</v>
+        <v>6.841851114113659</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>10.74627212337994</v>
+        <v>10.75972441210005</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>9.355143726027272</v>
+        <v>9.368699772378875</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.60486505830356</v>
+        <v>9.594435422605407</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>119</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.489754957100956</v>
+        <v>5.502277246776579</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.558853613044256</v>
+        <v>5.571763422620307</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.365665578716566</v>
+        <v>9.378672710134168</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.495918711324066</v>
+        <v>9.50889785372253</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8.117161361798118</v>
+        <v>8.130272166173057</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.532250358337308</v>
+        <v>2.545293254631673</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.60718050661125</v>
+        <v>1.620246760911726</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.501341645644878</v>
+        <v>4.514522654940116</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.600005625008798</v>
+        <v>3.613204363963561</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.430552708888428</v>
+        <v>4.443957836541259</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.906471653478413</v>
+        <v>5.91992894718863</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8.461863214185186</v>
+        <v>8.475315502905296</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>7.201272468786499</v>
+        <v>7.214828515138102</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.291329935516572</v>
+        <v>8.28090029981842</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>152</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.059193258737395</v>
+        <v>6.071715548413017</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6.421303856299453</v>
+        <v>6.434213665875504</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9.31590883391339</v>
+        <v>9.328915965330992</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.130372492836678</v>
+        <v>8.143351635235142</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7.591951277764508</v>
+        <v>7.605062082139447</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.626235320743319</v>
+        <v>2.639278217037685</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.0900773438973772</v>
+        <v>-0.07701108959690117</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.416423467847437</v>
+        <v>1.429604477142675</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.013318318507238</v>
+        <v>2.026517057462002</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.794772080847743</v>
+        <v>3.808177208500574</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.932124019688047</v>
+        <v>2.945581313398264</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.913875598086115</v>
+        <v>6.927327886806225</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.519936776614898</v>
+        <v>4.533492822966501</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.085447582575398</v>
+        <v>6.075017946877246</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>214</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.983197193808721</v>
+        <v>4.995719483484343</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.708072178975293</v>
+        <v>5.720981988551344</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9.518810949014224</v>
+        <v>9.531818080431826</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.181774361995551</v>
+        <v>9.194753504394015</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.306904548792545</v>
+        <v>6.320015353167484</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.464159570620353</v>
+        <v>1.477202466914719</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4448464140957356</v>
+        <v>0.4579126683962116</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.9122424545665737</v>
+        <v>0.9254234638618115</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.8512425683842721</v>
+        <v>0.8644413073390353</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.337565981487188</v>
+        <v>2.350971109140019</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.198233217917277</v>
+        <v>1.211690511627495</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.503644412645876</v>
+        <v>4.517096701365986</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.214230923196304</v>
+        <v>2.227786969547907</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.996662535846426</v>
+        <v>1.986232900148273</v>
       </c>
     </row>
     <row r="11">
@@ -4171,514 +4171,514 @@
         <v>284</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.605153229085801</v>
+        <v>5.617675518761423</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.641466940065207</v>
+        <v>3.654376749641258</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7.11983767008833</v>
+        <v>7.132844801505932</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.954316154808502</v>
+        <v>7.967295297206967</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.303218883398308</v>
+        <v>5.316329687773248</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.135872088719609</v>
+        <v>3.148914985013974</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.34691301933465</v>
+        <v>2.359979273635126</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.527616944496813</v>
+        <v>1.540797953792051</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7623917062018393</v>
+        <v>0.7755904451566025</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.9686045493429205</v>
+        <v>0.9820096769957516</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.2924868031436674</v>
+        <v>-0.2790295094334496</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.502459734483452</v>
+        <v>1.515912023203562</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.3262455806868019</v>
+        <v>-0.312689534335199</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.627701103702158</v>
+        <v>0.6172714680040059</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.09909</t>
+          <t>X &lt; -0.09907</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>364</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.924144097372441</v>
+        <v>4.936666387048064</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.938944110781812</v>
+        <v>1.951853920357863</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.566053426163244</v>
+        <v>4.579060557580846</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.696306558770743</v>
+        <v>4.709285701169208</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.058984244797479</v>
+        <v>3.072095049172418</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3344481605351177</v>
+        <v>0.3474910568294831</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2497144432628389</v>
+        <v>0.2627806975633149</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.041644779694494</v>
+        <v>-1.028463770399256</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.652095215327343</v>
+        <v>-1.63889647637258</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.227495125629993</v>
+        <v>-2.214089997977162</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.98169899939812</v>
+        <v>-2.968241705687902</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.123140017876871</v>
+        <v>-2.109687729156761</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.191746277173415</v>
+        <v>-4.178190230821812</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.216750219622398</v>
+        <v>-4.22717985532055</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.08411</t>
+          <t>X &lt; -0.08409</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>450</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.617672790901139</v>
+        <v>2.630195080576762</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.450543622381325</v>
+        <v>1.463453431957376</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.277897138006949</v>
+        <v>3.290904269424551</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.408150270614449</v>
+        <v>3.421129413012913</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.425284611097844</v>
+        <v>2.438395415472783</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.389393215480176</v>
+        <v>1.402436111774541</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4157706093190043</v>
+        <v>0.4288368636194804</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.05141278946249628</v>
+        <v>-0.03823178016725848</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.7790793423114692</v>
+        <v>-0.765880603356706</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.629204527339397</v>
+        <v>-1.615799399686566</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.278402296101419</v>
+        <v>-2.264945002391201</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.021796916533759</v>
+        <v>-2.008344627813649</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.330940416367554</v>
+        <v>-3.317384370015951</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.525663528535716</v>
+        <v>-3.536093164233868</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.06913</t>
+          <t>X &lt; -0.06912</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>574</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.9908822372813191</v>
+        <v>1.003404526956942</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.9472528751881413</v>
+        <v>0.9601626847641924</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.771896363713502</v>
+        <v>1.784903495131104</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.553717440571866</v>
+        <v>1.56669658297033</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.583240476370783</v>
+        <v>2.596351280745722</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.661170218964493</v>
+        <v>1.674213115258858</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.8795723901939496</v>
+        <v>0.8926386444944256</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.4586911479603728</v>
+        <v>-0.445510138665135</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.739203229264618</v>
+        <v>-1.726004490309855</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.111976497916245</v>
+        <v>-3.098571370263414</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.316729822233825</v>
+        <v>-3.303272528523607</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.979210776386644</v>
+        <v>-3.965758487666534</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.702601275833295</v>
+        <v>-3.689045229481692</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.323960082929823</v>
+        <v>-4.334389718627975</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.05415</t>
+          <t>X &lt; -0.05414</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.131764905904987</v>
+        <v>-0.05504001975268125</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.01104744604304386</v>
+        <v>0.08579545052580784</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.640470237422157</v>
+        <v>1.712587408088822</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.715392735751649</v>
+        <v>2.786208778092281</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.851735353338057</v>
+        <v>2.921773672435947</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.720027493482867</v>
+        <v>0.7932716912893625</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.500341009678877</v>
+        <v>0.4390195530474514</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.046464521356334</v>
+        <v>-1.106216206642252</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.512322707133784</v>
+        <v>-1.571511031628638</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.307117257883704</v>
+        <v>-3.364826054373594</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.511870582201283</v>
+        <v>-3.569527212633787</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.152251257514422</v>
+        <v>-4.209003507717824</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.032694802332472</v>
+        <v>-4.090070803079747</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.457737302714747</v>
+        <v>-4.538189600292569</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.03917</t>
+          <t>X &lt; -0.03916</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.6541364991914662</v>
+        <v>0.6118674746202899</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.384152153513071</v>
+        <v>0.3970619630891221</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.537271063015559</v>
+        <v>1.550278194433162</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.564325021216447</v>
+        <v>1.577304163614912</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.954696375803721</v>
+        <v>1.96780718017866</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.323345743859939</v>
+        <v>1.336388640154304</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.413018631334829</v>
+        <v>0.426084885635305</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.086156511512726</v>
+        <v>-1.072975502217488</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.9407580488818184</v>
+        <v>-0.9275593099270552</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.997281582722955</v>
+        <v>-1.983876455070124</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.511632430260349</v>
+        <v>-2.498175136550131</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.096444319354546</v>
+        <v>-3.082992030634436</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.794304709453208</v>
+        <v>-2.780748663101605</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.005461508333696</v>
+        <v>-2.967809710501491</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.02419</t>
+          <t>X &lt; -0.02418</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.571077808822281</v>
+        <v>0.5408406173302751</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6972479538314147</v>
+        <v>0.6659623925308509</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.396726791570053</v>
+        <v>1.364619631275509</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.123102702852826</v>
+        <v>1.13608184525129</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.634762263224928</v>
+        <v>1.647873067599868</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.528326979615869</v>
+        <v>1.541369875910235</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.039716041018877</v>
+        <v>1.052782295319354</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.3159972446769999</v>
+        <v>-0.3028162353817621</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.0268800904654114</v>
+        <v>0.0400788294201746</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.6616942060326281</v>
+        <v>-0.648289078379797</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.189549307409976</v>
+        <v>-1.176092013699758</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.124471481243873</v>
+        <v>-2.111019192523763</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.140848870864055</v>
+        <v>-2.127292824512452</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.766209652671172</v>
+        <v>-1.740006285756039</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.009211</t>
+          <t>X &lt; -0.009202</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.3495777490112886</v>
+        <v>0.3294607452531721</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5641284502518644</v>
+        <v>0.5432501631756139</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.316951043397502</v>
+        <v>1.295439416816841</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.014035859173312</v>
+        <v>1.027015001571776</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.341951277764508</v>
+        <v>1.355062082139447</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.921900955418245</v>
+        <v>1.899960864249785</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.341811200994272</v>
+        <v>1.354877455294748</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.750788792924844</v>
+        <v>0.7639698022200818</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.4421108881666882</v>
+        <v>0.4553096271214514</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3460947922172792</v>
+        <v>-0.3326896645644482</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7985261351107056</v>
+        <v>-0.7850688414004878</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.631016042780757</v>
+        <v>-1.617563754060647</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.617834121217918</v>
+        <v>-1.604278074866315</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.457922925479124</v>
+        <v>-1.440461929283742</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.005769</t>
+          <t>X &lt; 0.005777</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1610768041749893</v>
+        <v>-0.1739709115445507</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.240160207359942</v>
+        <v>-0.2534237951239362</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6557613835754879</v>
+        <v>0.6419548825072567</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8128542446614944</v>
+        <v>0.7989936585814519</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.080266759750884</v>
+        <v>1.066132641750151</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.453689367452895</v>
+        <v>1.439437085484371</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.076700413940969</v>
+        <v>1.089766668241445</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.706935427239344</v>
+        <v>0.7201164365345818</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4998079229372223</v>
+        <v>0.5130066618919855</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.2528988500108298</v>
+        <v>-0.2394937223579987</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3602337622485194</v>
+        <v>-0.3467764685383017</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.105197901542155</v>
+        <v>-1.091745612822045</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.059985250675545</v>
+        <v>-1.073513611775979</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.124450028346104</v>
+        <v>-1.113091214916132</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.02075</t>
+          <t>X &lt; 0.02076</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.7062734136299582</v>
+        <v>-0.71477717547954</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4276450091596047</v>
+        <v>-0.4365375419572359</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.5407697667332414</v>
+        <v>0.5314117415451918</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3274038063787685</v>
+        <v>0.3181483832026188</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6249048985944441</v>
+        <v>0.6154321512732466</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.026348852435802</v>
+        <v>1.016756697616685</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5346147281631204</v>
+        <v>0.5476809824635964</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.06743132938161978</v>
+        <v>0.08061233867685758</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2377688010009251</v>
+        <v>-0.2245700620461619</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.5994934976283659</v>
+        <v>-0.5860883699755348</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7228467405458616</v>
+        <v>-0.7093894468356439</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.543164437901282</v>
+        <v>-1.529712149181172</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.289680915824668</v>
+        <v>-1.298662351293935</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.424735716813608</v>
+        <v>-1.416838730647186</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2780</v>
+        <v>2781</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.7890967342752759</v>
+        <v>-0.7951197608069478</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.4797427300155803</v>
+        <v>-0.486074136515299</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1141229508934529</v>
+        <v>0.1075270659468543</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.1562345618021936</v>
+        <v>0.149635297712706</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.3560547632118656</v>
+        <v>0.3493149557026598</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.6374162205125202</v>
+        <v>0.6306071502222466</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.301064961903073</v>
+        <v>0.314131216203549</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.2020637999265986</v>
+        <v>-0.1888827906313608</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5146812274460686</v>
+        <v>-0.5014824884913054</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.502117699317985</v>
+        <v>-0.4887125716651539</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.8865978388764049</v>
+        <v>-0.8731405451661871</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.247613675060805</v>
+        <v>-1.234161386340695</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.180634770916278</v>
+        <v>-1.187022520027938</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.9828977411656155</v>
+        <v>-0.9773013627236153</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3054</v>
+        <v>3056</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.3564073251039375</v>
+        <v>-0.377883751434247</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2864740741663994</v>
+        <v>-0.2760551568662777</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.043465360632716</v>
+        <v>-0.03336616740705978</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.1045723622031005</v>
+        <v>0.1146310086032827</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1066523558435719</v>
+        <v>0.1164887879833927</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.1933147841076277</v>
+        <v>0.2032199132115053</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.2330979388630467</v>
+        <v>-0.2229472301770272</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6349004942316725</v>
+        <v>-0.6068592311476593</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.9396781360037849</v>
+        <v>-0.9292792961671665</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.8561154421796502</v>
+        <v>-0.8788120036602649</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.126292384423301</v>
+        <v>-1.098169332018408</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.401087201583209</v>
+        <v>-1.390802298041116</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.214191916640331</v>
+        <v>-1.204201511003845</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.011801926265463</v>
+        <v>-1.025767393436887</v>
       </c>
     </row>
     <row r="23">
@@ -4792,153 +4792,153 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3249</v>
+        <v>3250</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7153880443056195</v>
+        <v>-0.7187339894678431</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.9004734480469736</v>
+        <v>-0.9038740426662386</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.818899044678794</v>
+        <v>-0.8223534224899893</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.6721743006582557</v>
+        <v>-0.67566676967283</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5188528965755737</v>
+        <v>-0.5224310139022776</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.4503365972309155</v>
+        <v>-0.4539174793856944</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.7641365705881782</v>
+        <v>-0.7676288683083357</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.9382535472710032</v>
+        <v>-0.9417261836616575</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.166977996958742</v>
+        <v>-1.170386491733559</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.20122351835623</v>
+        <v>-1.204681459373788</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.512104633124792</v>
+        <v>-1.515482967346628</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.799232919131256</v>
+        <v>-1.80252256959308</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.556581442008579</v>
+        <v>-1.559976392983245</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.25911997667361</v>
+        <v>-1.255751283891982</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.08066</t>
+          <t>X &lt; 0.08067</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3414</v>
+        <v>3415</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.640505726104351</v>
+        <v>-0.6431097294841805</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7483277533727133</v>
+        <v>-0.7509874460376267</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.9232383040043999</v>
+        <v>-0.9258694219550847</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.8649546099670644</v>
+        <v>-0.867597269874345</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.7450338230242792</v>
+        <v>-0.747741656178313</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.6947680936957497</v>
+        <v>-0.6974762458065413</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.9391288677669678</v>
+        <v>-0.9417716174507262</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.156675947357229</v>
+        <v>-1.159281505718603</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.318873304158664</v>
+        <v>-1.321436158912263</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.246264536441529</v>
+        <v>-1.248895496660985</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.493503261860852</v>
+        <v>-1.49607431778032</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.706548412760668</v>
+        <v>-1.709056753459933</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.64231181705081</v>
+        <v>-1.644862902412513</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.347182763060218</v>
+        <v>-1.34445496673915</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.09564</t>
+          <t>X &lt; 0.09565</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3567</v>
+        <v>3568</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.5381310576401503</v>
+        <v>-0.5401173709420632</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.6822681499945702</v>
+        <v>-0.6842808945479035</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7827202149524908</v>
+        <v>-0.7847220694037915</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.8331444207780905</v>
+        <v>-0.8351279623053784</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.6854536439357162</v>
+        <v>-0.6875015186433302</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.652564826477871</v>
+        <v>-0.6546108680912326</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.9740198526594881</v>
+        <v>-0.9759805411979272</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.9783649305204349</v>
+        <v>-0.9803445700696471</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.024195679253111</v>
+        <v>-1.026166077747973</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.075049139804008</v>
+        <v>-1.077041156561023</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.236385489378726</v>
+        <v>-1.238341810008116</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.410732503844251</v>
+        <v>-1.412639679167526</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.33916164207757</v>
+        <v>-1.341107168185374</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.101964808789887</v>
+        <v>-1.099869945499435</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3657</v>
+        <v>3658</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.6678252411909043</v>
+        <v>-0.6694205252224563</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.7662275232532707</v>
+        <v>-0.7678514423992695</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9011892548198972</v>
+        <v>-0.9027906519890863</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9472113631764145</v>
+        <v>-0.9487966744704224</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.7618403207079396</v>
+        <v>-0.7634953217329326</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8589014639195582</v>
+        <v>-0.8605207894802334</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.092720414455869</v>
+        <v>-1.094279704517554</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.026569764619474</v>
+        <v>-1.028163851977055</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.127401449235428</v>
+        <v>-1.128970966447064</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.088672189483916</v>
+        <v>-1.090282074606165</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.223757487358249</v>
+        <v>-1.225338337545523</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.310977324052509</v>
+        <v>-1.312534063150629</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.224142530455396</v>
+        <v>-1.22573820075295</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.095985285896028</v>
+        <v>-1.094200205118383</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3746</v>
+        <v>3747</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5115282377412314</v>
+        <v>-0.5128309241513733</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3796260896404391</v>
+        <v>-0.381008747700335</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.5738758487141311</v>
+        <v>-0.5752183726427447</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.6422579650972935</v>
+        <v>-0.6435794267824235</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.60711663168955</v>
+        <v>-0.6084629444846215</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.7480601675778971</v>
+        <v>-0.7493614914212117</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8450873709634337</v>
+        <v>-0.8463658830803311</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.7915217683774429</v>
+        <v>-0.7928281031089099</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.8913457009121402</v>
+        <v>-0.8926278196561555</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.7669823051171676</v>
+        <v>-0.7683216900387677</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.9036356916735713</v>
+        <v>-0.9049450023912016</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.06792522200039</v>
+        <v>-1.069190483004668</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.9663821030502362</v>
+        <v>-0.9676867535093692</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9420484131533726</v>
+        <v>-0.9405945431147487</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3815</v>
+        <v>3816</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.4819440673364142</v>
+        <v>-0.4830053488942383</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.43372894388758</v>
+        <v>-0.4348398456462448</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6316109063677899</v>
+        <v>-0.632679622803181</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7487124744835825</v>
+        <v>-0.7497482079431137</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.7239483038254519</v>
+        <v>-0.7250032773376773</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.7785377288044302</v>
+        <v>-0.7795722564262988</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.8753509675168587</v>
+        <v>-0.8763626597333314</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7788547040282054</v>
+        <v>-0.7799028075525811</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.8779740485360108</v>
+        <v>-0.8789981700204663</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.7973986444730201</v>
+        <v>-0.7984637394189633</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.8829072725288682</v>
+        <v>-0.8839552144886085</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.017401376115174</v>
+        <v>-1.018413890371129</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.9776909404765703</v>
+        <v>-0.9787239910097583</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8706467817758394</v>
+        <v>-0.869426497567197</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3887</v>
+        <v>3888</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.2883101150817708</v>
+        <v>-0.2891703243051751</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.3989334515122636</v>
+        <v>-0.3997944312904878</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3695573970822608</v>
+        <v>-0.3704333955037669</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5846647152721189</v>
+        <v>-0.5854836649187831</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5445990302437096</v>
+        <v>-0.5454383027720269</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6696568487046761</v>
+        <v>-0.6704591654328595</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.7405382419051065</v>
+        <v>-0.7413243116764789</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5516839313981734</v>
+        <v>-0.5525272775136045</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6500397168689673</v>
+        <v>-0.6508593401206966</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.560927306402192</v>
+        <v>-0.5617854679747865</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.6742891855615767</v>
+        <v>-0.6751223346965247</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.7798895424587329</v>
+        <v>-0.7806953847402482</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.7743560542276455</v>
+        <v>-0.7751712903896575</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.6903435159581832</v>
+        <v>-0.689385345303819</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3938</v>
+        <v>3939</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1522588719690248</v>
+        <v>-0.1529808078622921</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2315942116552421</v>
+        <v>-0.2323197900117435</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2583004928981936</v>
+        <v>-0.2590254070873996</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4182597260083085</v>
+        <v>-0.4189426164741477</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.385626629506838</v>
+        <v>-0.3863259624400897</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4544993339369654</v>
+        <v>-0.4551772654740063</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5255052673180955</v>
+        <v>-0.5261667969087682</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.4211445902287849</v>
+        <v>-0.4218397227105655</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4936226962157093</v>
+        <v>-0.4943007070303622</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.4419899154672464</v>
+        <v>-0.4426937553661077</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.6326271121379534</v>
+        <v>-0.6332859460746079</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.6856435042382216</v>
+        <v>-0.6862887480313162</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.736373267344959</v>
+        <v>-0.73701211959294</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6755986337780868</v>
+        <v>-0.6747916494670037</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3972</v>
+        <v>3973</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.07185739172817307</v>
+        <v>-0.07248652727294314</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1642488809653955</v>
+        <v>-0.1648750219670632</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.2442943982443353</v>
+        <v>-0.24490563686728</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.3515461410156604</v>
+        <v>-0.352129158136691</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2735347810146962</v>
+        <v>-0.2741443467907416</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3392500006002308</v>
+        <v>-0.3398396983234306</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.43547621428268</v>
+        <v>-0.4360430917127474</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.3611161579893931</v>
+        <v>-0.3617078070863613</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.433481040967628</v>
+        <v>-0.4340555656493095</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.3643934385846421</v>
+        <v>-0.3649961700047868</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5802890885542453</v>
+        <v>-0.5808403746246071</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.5822174276336938</v>
+        <v>-0.5827681078975147</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6360834652810539</v>
+        <v>-0.6366261079793816</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.5988424476360805</v>
+        <v>-0.5981509431303067</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4020</v>
+        <v>4021</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.07288947547561975</v>
+        <v>0.07238094517214932</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.03755161571391596</v>
+        <v>-0.03804806954412498</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.02208356708415238</v>
+        <v>-0.02258779406751188</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1512652242849128</v>
+        <v>-0.1517364322419112</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.03090799252588283</v>
+        <v>-0.03141434465955939</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.01775673486739748</v>
+        <v>-0.0182638137652944</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.1882632730858731</v>
+        <v>-0.188729063777636</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1948140148309321</v>
+        <v>-0.195282796915329</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2173126066316939</v>
+        <v>-0.2177766126297627</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1839869439508419</v>
+        <v>-0.1844674466154785</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3499906629918001</v>
+        <v>-0.3504320799259943</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.4260181442259068</v>
+        <v>-0.4264405761109415</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4344801660152413</v>
+        <v>-0.4349046750051784</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.3946519199121568</v>
+        <v>-0.3941439531476192</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1070053573843026</v>
+        <v>0.1065654874548017</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.01230976354898417</v>
+        <v>-0.01273313173227564</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.05005770794804221</v>
+        <v>0.04961564352054637</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.07757027973362085</v>
+        <v>-0.07798005403736141</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.06357723384642355</v>
+        <v>0.06312818968754641</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.05375649287405082</v>
+        <v>0.05331200617374066</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.09153897130581612</v>
+        <v>-0.09194848243733844</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1254868635365725</v>
+        <v>-0.1258918915252281</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1234990892997487</v>
+        <v>-0.1239052947147243</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.07068454490637066</v>
+        <v>-0.07111072484229197</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2121804033413497</v>
+        <v>-0.2125734608892245</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2628031229378962</v>
+        <v>-0.2631836031863557</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.2983899425315428</v>
+        <v>-0.2987651576251125</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2572823877510118</v>
+        <v>-0.2568732768557567</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4066</v>
+        <v>4067</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.142011544953057</v>
+        <v>0.1416329890734929</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.03917639443734089</v>
+        <v>0.0388123162154983</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.07456135188971302</v>
+        <v>0.07418583446189331</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.04646670284649446</v>
+        <v>0.04609875321405354</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1348960630405784</v>
+        <v>0.1345027102061778</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1512979773849352</v>
+        <v>0.1509023694432514</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.006353581193408786</v>
+        <v>0.005992811909450779</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.02991093397243105</v>
+        <v>-0.03026604374583997</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.02824007268075235</v>
+        <v>-0.02859616764398254</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.01971712158225358</v>
+        <v>0.0193434808505657</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.07294641013434955</v>
+        <v>-0.07329881074500832</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1722393944098712</v>
+        <v>-0.1725673415571407</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2098847651914255</v>
+        <v>-0.2102063955813378</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1430324961260254</v>
+        <v>-0.1427101082002054</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4087</v>
+        <v>4088</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.04314704564368554</v>
+        <v>0.04285865856586923</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1521239536274237</v>
+        <v>0.1518003154262146</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.112125216744559</v>
+        <v>0.1118090971603181</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1336675868078743</v>
+        <v>0.1333467548056646</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1944903402645082</v>
+        <v>0.1941516598792603</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2367680628550204</v>
+        <v>0.2364204867745343</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.0921533917105819</v>
+        <v>0.09184052662314457</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.0536989188742254</v>
+        <v>0.05339281951791719</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.006192733283185703</v>
+        <v>0.005897771646687033</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.09843609299249323</v>
+        <v>0.09811392712998668</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.04368346969554437</v>
+        <v>-0.04397213512158515</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1422827728963654</v>
+        <v>-0.1425472901336775</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1329625951020574</v>
+        <v>-0.1332317654671584</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.06515187913245057</v>
+        <v>-0.06490377523626023</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/roc/roc_7.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_7.xlsx
@@ -568,1093 +568,1093 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.1815</t>
+          <t>X ≈ -0.1813</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>19</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-10.34332712655906</v>
+        <v>-10.37251309949142</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.038792510384809</v>
+        <v>9.037682776302582</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.397858754114857</v>
+        <v>3.397734866261366</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.77909895401541</v>
+        <v>8.77866678563305</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8.244287369904178</v>
+        <v>8.292775452738233</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.96228609834619</v>
+        <v>-1.938386140087438</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-7.301344569937356</v>
+        <v>-7.253450472947122</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.514193979498103</v>
+        <v>-2.465029580948084</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.681154452545286</v>
+        <v>2.754328579930259</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.425345327641928</v>
+        <v>-3.326106278045827</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>12.14713736701019</v>
+        <v>12.24699457194919</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.18443882345162</v>
+        <v>12.30808994405395</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.76742223658725</v>
+        <v>11.91608244746225</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>17.25922847319303</v>
+        <v>17.43122723275969</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.1665</t>
+          <t>X ≈ -0.1663</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>16</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.473553436896303</v>
+        <v>-2.502671973377367</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-10.3120420214787</v>
+        <v>-10.31330508368276</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-10.70867879050532</v>
+        <v>-10.70890553963606</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.346601889713163</v>
+        <v>-4.347120447755827</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.884614845537904</v>
+        <v>-4.836205560164466</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-10.82633682826219</v>
+        <v>-10.80248471410057</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.674194994672163</v>
+        <v>-4.62628994024773</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.141852152679014</v>
+        <v>-5.092699065982963</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.280715214491892</v>
+        <v>7.353904043760743</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1895367801307941</v>
+        <v>0.2887844675636728</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.01499041281648772</v>
+        <v>0.08484221566916972</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.227580402026099</v>
+        <v>-6.103954111725763</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.649111621326355</v>
+        <v>-6.50046389096952</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1749820531227542</v>
+        <v>-0.002983293556091837</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.1515</t>
+          <t>X ≈ -0.1513</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.098408974077778</v>
+        <v>9.224297281748655</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.515501322566401</v>
+        <v>10.58073377670221</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.123760643718121</v>
+        <v>10.1902807880757</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.210479433323499</v>
+        <v>4.454692584391935</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>5.697879437633134</v>
+        <v>6.902411431118914</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.972219671360278</v>
+        <v>4.24144287818855</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-6.186614465128422</v>
+        <v>-4.626191195784358</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-9.68044137934065</v>
+        <v>-8.029411494952249</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.690596570906862</v>
+        <v>-2.193186470349126</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.513973834092816</v>
+        <v>2.85975808649188</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.774351913190877</v>
+        <v>-6.160510137641722</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.344446398194336</v>
+        <v>2.71523471150963</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-5.134317344053798</v>
+        <v>-3.559997656860425</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.879527507668215</v>
+        <v>-0.3706303523796208</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.1365</t>
+          <t>X ≈ -0.1363</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>62</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2.349299213889424</v>
+        <v>0.7125511296131037</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.959807455541757</v>
+        <v>2.350583097197742</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.00047194025203</v>
+        <v>8.391918298893813</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>11.74199187376848</v>
+        <v>10.13269979228041</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.161783861913513</v>
+        <v>1.600958180759868</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.369100066637309</v>
+        <v>-2.95487975538579</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.766344082461927</v>
+        <v>0.2041924147273448</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.3101371867088005</v>
+        <v>-1.871453058986368</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.981990199502462</v>
+        <v>-3.519722728987638</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.220347688344049</v>
+        <v>-2.732397172146122</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.036846896815405</v>
+        <v>-4.548715986154029</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.391237009061818</v>
+        <v>-1.26761200262704</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.424064533062477</v>
+        <v>-4.88791558293353</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-8.037885278929203</v>
+        <v>-9.478789745168996</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.1215</t>
+          <t>X ≈ -0.1214</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7.493102215437531</v>
+        <v>8.330803591179738</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.65614563676035</v>
+        <v>-1.914250912143082</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2020548531834194</v>
+        <v>0.5823730438376344</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.202747420146046</v>
+        <v>5.049015865957116</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.241989406601107</v>
+        <v>3.116717745926685</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>8.242549501518425</v>
+        <v>9.175639123242227</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>8.160260687637781</v>
+        <v>9.117587617179737</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.416847028877157</v>
+        <v>4.313607704722401</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.5033786989387892</v>
+        <v>1.38297529661412</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.199837714575004</v>
+        <v>-2.335332091791486</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.832618490560876</v>
+        <v>-3.988022750651574</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-7.655274818445434</v>
+        <v>-8.27662100772001</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-8.077216868185346</v>
+        <v>-7.22481649878813</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.567839195979253</v>
+        <v>-2.629794887758329</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.1066</t>
+          <t>X ≈ -0.1064</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.509093510097991</v>
+        <v>1.803326011957139</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.079939417194339</v>
+        <v>-4.696501925273765</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.475460023275069</v>
+        <v>-3.860127900821965</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.840155910910774</v>
+        <v>-6.194233012526084</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.884258817857535</v>
+        <v>-4.220028771498122</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-9.577826394736405</v>
+        <v>-8.876380762223334</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-7.169278287015047</v>
+        <v>-7.706741048809263</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-10.13343765850949</v>
+        <v>-10.63899841478539</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-10.19688022976075</v>
+        <v>-10.67859035744956</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-13.54598422798912</v>
+        <v>-13.97092825481759</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-12.50499758725711</v>
+        <v>-12.94489953217256</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-14.97270801555215</v>
+        <v>-15.35809417843645</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-17.89598535346794</v>
+        <v>-18.22561992332876</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-21.42498205312332</v>
+        <v>-21.68508205898875</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.09158</t>
+          <t>X ≈ -0.09144</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>86</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-7.108921569750279</v>
+        <v>-5.979261810901932</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.6022372373621181</v>
+        <v>0.5556863986570164</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-2.156223861471922</v>
+        <v>-2.156421842426774</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.026771210795665</v>
+        <v>-2.027304610103812</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2438405285041227</v>
+        <v>-0.1954492285230529</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.854999131970473</v>
+        <v>5.878908412223666</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.129646951161213</v>
+        <v>2.338205731987941</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.146577385104479</v>
+        <v>5.356702026427797</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.925625988915932</v>
+        <v>4.160038472316892</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.9158539246535327</v>
+        <v>2.176646823093506</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.7115374815682003</v>
+        <v>0.8113691724775194</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.578392098930181</v>
+        <v>-1.454763437359105</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.326074122908004</v>
+        <v>0.4747234527201272</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.6110285647511944</v>
+        <v>-0.4390298051839991</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.07661</t>
+          <t>X ≈ -0.07648</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>124</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-4.883801648934764</v>
+        <v>-4.91296772196651</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.8638432460098855</v>
+        <v>-0.8650719004145486</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.670428523267155</v>
+        <v>-3.670642700768937</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-5.149873387730814</v>
+        <v>-5.150433729760451</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3.160992179298859</v>
+        <v>3.209398059360126</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.654331237510206</v>
+        <v>2.678220068175548</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.570835494025872</v>
+        <v>2.618732928383352</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.920198681212781</v>
+        <v>-1.871072415036998</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.202822281831246</v>
+        <v>-5.12971705594164</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-8.469848473654018</v>
+        <v>-8.370665564034368</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-7.065189383762949</v>
+        <v>-6.159598430173318</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-11.06293338465186</v>
+        <v>-10.13331861891394</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-5.036273687733896</v>
+        <v>-4.081402678208313</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-7.231433666025247</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.06163</t>
+          <t>X ≈ -0.0615</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.658166221757611</v>
+        <v>-4.36664587043623</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.891869593283168</v>
+        <v>-3.60648342575535</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.459898619739903</v>
+        <v>1.970502541877259</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6.932003898079266</v>
+        <v>7.484380373003553</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.022057185437824</v>
+        <v>4.595772838141229</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-2.211956163784734</v>
+        <v>-1.382850803220371</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.108712973971812</v>
+        <v>-0.5238794287051007</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-3.357492483181801</v>
+        <v>-3.06320618520175</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.041582842433691</v>
+        <v>-0.9767992132638099</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.268848427684262</v>
+        <v>-4.458042321450328</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.474760737137409</v>
+        <v>-4.663436926449002</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.036721343690573</v>
+        <v>-5.205229981624925</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-5.458446471341794</v>
+        <v>-5.602004561205206</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-5.234505862646969</v>
+        <v>-5.354779700741716</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.04665</t>
+          <t>X ≈ -0.04653</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.78406639568135</v>
+        <v>2.25667516941256</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.409350846648074</v>
+        <v>1.091262224596846</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.014961943376356</v>
+        <v>-0.1738336878918503</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.368677568300647</v>
+        <v>-2.65818601983274</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.148918717237642</v>
+        <v>-1.844201821101187</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.103640118377051</v>
+        <v>2.354893657304586</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.3829408221086936</v>
+        <v>-0.3272610306209387</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9619155240486137</v>
+        <v>-0.8034851833149403</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.176209593479371</v>
+        <v>0.9034967284755311</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.527958213646343</v>
+        <v>2.683352930971139</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.003667474481126</v>
+        <v>0.9787980708670645</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.5978934729986136</v>
+        <v>0.4125189717158904</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.498906305406564</v>
+        <v>1.139838672183537</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.165326316921401</v>
+        <v>1.388938103823925</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.03167</t>
+          <t>X ≈ -0.03156</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>269</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2885433549075529</v>
+        <v>0.4542288114720918</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.63424323230165</v>
+        <v>1.466261628815602</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.6986726211499175</v>
+        <v>0.7015768965721421</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4532936007196042</v>
+        <v>-1.025686544153828</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4921464626446408</v>
+        <v>-0.02958712662118756</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.272617964821478</v>
+        <v>2.102165853614395</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.302315376936932</v>
+        <v>3.155362988454279</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.467274264178869</v>
+        <v>1.942796177160211</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.520417849733256</v>
+        <v>3.392581013669862</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.158119651096214</v>
+        <v>3.679828833675444</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.583589571509869</v>
+        <v>3.474299974517052</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.390022569835715</v>
+        <v>1.301520636632347</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.2268572183362636</v>
+        <v>0.1617112765912481</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.682824638327062</v>
+        <v>2.854823397893725</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.01669</t>
+          <t>X ≈ -0.01659</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3644055054444095</v>
+        <v>-0.2909424792299831</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.1403905507133771</v>
+        <v>0.4770610318943014</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.067256736989364</v>
+        <v>0.8685630436025207</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.6688385938512766</v>
+        <v>0.4754743748170256</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3955639338560673</v>
+        <v>0.3892100961460656</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.074083210669031</v>
+        <v>3.018016557373365</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.339548782096792</v>
+        <v>2.433800258723814</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.257639690401362</v>
+        <v>4.585768545460887</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.815526681057449</v>
+        <v>2.192774993915783</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.7032180955637983</v>
+        <v>1.107166308388692</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4991340843251635</v>
+        <v>0.9030258608526012</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.003653139503157377</v>
+        <v>0.4376323887933538</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1135673727915858</v>
+        <v>0.8278147763657131</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4568122918495447</v>
+        <v>-0.2320408851791882</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001713</t>
+          <t>X ≈ -0.001618</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.03363598212345</v>
+        <v>-2.050833050895747</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-3.194719679484542</v>
+        <v>-3.40538495985362</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.763366761658773</v>
+        <v>-1.518623590866454</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.03614523720688823</v>
+        <v>0.437377690802343</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.003990407857436651</v>
+        <v>0.1764390521335386</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.260132681588523</v>
+        <v>-0.2357069358968076</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.1117841222386105</v>
+        <v>-0.06805252283920993</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5583546950331737</v>
+        <v>0.1510462236268069</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7260934495053917</v>
+        <v>0.1140736144899108</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.1039139663408619</v>
+        <v>-0.4814444640419708</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.270134893010905</v>
+        <v>0.6842781021206292</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.8464638531796354</v>
+        <v>0.05751333263624758</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.8828781586925913</v>
+        <v>-0.10933409164452</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.09675707731207694</v>
+        <v>-0.3169102341953547</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.01327</t>
+          <t>X ≈ 0.01335</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.458387327639336</v>
+        <v>-3.124629024417466</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.36341111308554</v>
+        <v>-0.9899347704689276</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.03351311041186733</v>
+        <v>0.3511418212484543</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.124068093354403</v>
+        <v>-1.999822757887252</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.674725113476626</v>
+        <v>-1.496516067573687</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.132819368664194</v>
+        <v>-0.9755915909384427</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.202540006486153</v>
+        <v>-2.028803511429359</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.161567773061734</v>
+        <v>-2.990914187445483</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-3.964192452673338</v>
+        <v>-3.524164712215004</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.342549149234941</v>
+        <v>-1.866603714866159</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.548496090572996</v>
+        <v>-2.070744162402306</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.752408642335567</v>
+        <v>-3.005133256302976</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.442796911270129</v>
+        <v>-1.663318478152107</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.959635518469341</v>
+        <v>-2.406829447402245</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.02824</t>
+          <t>X ≈ 0.02833</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>325</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.393653379607372</v>
+        <v>-1.901369864675175</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.8545073772651861</v>
+        <v>-1.337409199099859</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-3.092242404868664</v>
+        <v>-3.575302945378503</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.12279483592377</v>
+        <v>-1.741758241758319</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.660585560020621</v>
+        <v>-2.23100738271016</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.285815717057261</v>
+        <v>-2.573606479275853</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.447921889651703</v>
+        <v>-1.711185645424386</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.218109134666541</v>
+        <v>-2.484710713500078</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.585935617110081</v>
+        <v>-2.829375630329139</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.2492100357481561</v>
+        <v>0.03910348116357198</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.106282071906378</v>
+        <v>-2.318883120218679</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.001221085350039</v>
+        <v>0.8162066940692867</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.34302539565698</v>
+        <v>-0.5020281555714519</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.344248716108019</v>
+        <v>2.208555167982375</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.04322</t>
+          <t>X ≈ 0.0433</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>3.819849275974207</v>
+        <v>4.127308060198835</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.831096916046405</v>
+        <v>2.18260727845044</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.455714691973554</v>
+        <v>-1.249616826415057</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2347094423732159</v>
+        <v>-0.04059609455289603</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.226764952838785</v>
+        <v>-1.968694156368159</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.097281995691063</v>
+        <v>-4.213894249059983</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-5.643959796049359</v>
+        <v>-5.713399259148794</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.838509858115714</v>
+        <v>-5.100095328884613</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-5.275225999443713</v>
+        <v>-5.496780168237279</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.835272776157183</v>
+        <v>-5.241472058404781</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.381159263245451</v>
+        <v>-4.006763585077564</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.990493704790374</v>
+        <v>-3.588884617496845</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.377990430622013</v>
+        <v>-2.185481392981536</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.515891144031848</v>
+        <v>-2.296148761182025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.0582</t>
+          <t>X ≈ 0.05826</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-6.125126052111959</v>
+        <v>-5.605382684021855</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-10.84477165497786</v>
+        <v>-10.50354532029919</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-13.29678812023383</v>
+        <v>-12.94856535989612</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-13.16195238704319</v>
+        <v>-12.81868131868132</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-10.61299114250696</v>
+        <v>-10.23100738271016</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-10.82647044079543</v>
+        <v>-10.47104237671181</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-9.378620816290827</v>
+        <v>-8.993236927475671</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-6.253118042044704</v>
+        <v>-5.869326098115486</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.994356280207562</v>
+        <v>-4.880657681611254</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-6.363430767868181</v>
+        <v>-6.217306775246691</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-8.118676924236382</v>
+        <v>-7.959908761244321</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-8.29242252013897</v>
+        <v>-8.41456253669994</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-7.166181620875058</v>
+        <v>-7.271258924802225</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.87859030054544</v>
+        <v>-4.97093201150475</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.07318</t>
+          <t>X ≈ 0.07323</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>165</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.8524173027989832</v>
+        <v>0.8232215084463519</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.271534240038179</v>
+        <v>2.270347453593523</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.971721993201641</v>
+        <v>-2.971875383205962</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-4.659678667795163</v>
+        <v>-4.660173160173166</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-5.197968220890857</v>
+        <v>-5.149422301125085</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-5.506654797316372</v>
+        <v>-5.482697388366759</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-4.379243944461329</v>
+        <v>-4.331232265471009</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-5.452373194308713</v>
+        <v>-5.403125631914996</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.301234138710164</v>
+        <v>-4.227977028930468</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.120849904737064</v>
+        <v>-2.02150257944249</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.113429850876052</v>
+        <v>-1.013521814857377</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.133069513600482</v>
+        <v>0.2567661346287267</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.317384370015986</v>
+        <v>-3.168694822238159</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.091648719789418</v>
+        <v>-2.919649960222756</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.08816</t>
+          <t>X ≈ 0.08821</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.767449982537542</v>
+        <v>1.385992071216911</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.8098586607155482</v>
+        <v>1.101516284762361</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.375871589685993</v>
+        <v>2.006479595148953</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1082823516929636</v>
+        <v>-0.461038961038966</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.6606176376950046</v>
+        <v>0.3484131967104176</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.3043968960882992</v>
+        <v>-0.02815193382131298</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.741097776903395</v>
+        <v>-2.036859971098714</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.020591749244538</v>
+        <v>2.692112463323205</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.573988677689044</v>
+        <v>5.252542451588944</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.763285567633702</v>
+        <v>3.130012572072658</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.519368723099035</v>
+        <v>4.873924072588508</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.207341646696186</v>
+        <v>5.581441459304017</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.440785564624647</v>
+        <v>5.835634182090878</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.359331672367439</v>
+        <v>4.785977745404942</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.1031</t>
+          <t>X ≈ 0.1032</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-5.814249363867624</v>
+        <v>-5.31910058893186</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.655086662851829</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-5.597984619464334</v>
+        <v>-5.048824651166534</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-5.467759475875972</v>
+        <v>-4.918940609951854</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-3.783826806749445</v>
+        <v>-3.160998739667811</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-9.042008332669973</v>
+        <v>-8.506190748938771</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.793385358602677</v>
+        <v>-5.196060321310235</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.927120669056094</v>
+        <v>-2.291106564839716</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-5.210325047801085</v>
+        <v>-4.575270185212396</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.615799399686566</v>
+        <v>-2.028312249173517</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.7093894468357078</v>
+        <v>-1.108857191091623</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.658322038852944</v>
+        <v>2.320096063127266</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.349282296650713</v>
+        <v>3.048533642181475</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.869426497567197</v>
+        <v>-1.196803518275189</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.1181</t>
+          <t>X ≈ 0.1182</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>89</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5.946050261600412</v>
+        <v>5.916854467247781</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>15.57081922471643</v>
+        <v>15.56963243827177</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>12.92885682872544</v>
+        <v>12.92870343872112</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>11.93548646669584</v>
+        <v>11.93499197431784</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.779219385510174</v>
+        <v>5.827765305275946</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.829402403909363</v>
+        <v>3.853359812858976</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.362669572733026</v>
+        <v>9.410681251723346</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>8.895600928946287</v>
+        <v>8.944848491340004</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8.834618772423511</v>
+        <v>8.907875882203207</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>12.47908199856562</v>
+        <v>12.57842932386019</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>12.27438084030543</v>
+        <v>12.3742888763241</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>8.937972475806752</v>
+        <v>9.061669096834997</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>9.641417128111385</v>
+        <v>9.790106675889213</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.37277075586595</v>
+        <v>5.544769515432613</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>69</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.142272375262756</v>
+        <v>1.113076580910125</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-3.367464442438724</v>
+        <v>-3.36865122888338</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.762235827193841</v>
+        <v>-3.762389217198162</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-6.530561408243202</v>
+        <v>-6.531055900621205</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-7.068850961338725</v>
+        <v>-7.020305041572954</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.423650844747208</v>
+        <v>-2.399693435797595</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.508361204013333</v>
+        <v>-2.460349525023013</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.07687912316242773</v>
+        <v>-0.02763156076871098</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.1378612796852039</v>
+        <v>-0.06460416990550755</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.4370554383339</v>
+        <v>-2.337708113039326</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.256794128043623</v>
+        <v>0.3567021640622983</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.740447642717825</v>
+        <v>1.86414426374607</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.57825393523342</v>
+        <v>-1.429564387455592</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.995307801949828</v>
+        <v>3.16730656151649</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>10.01908396946565</v>
+        <v>10.50358680525</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.463453431957333</v>
+        <v>2.071094651600923</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>13.56868204720237</v>
+        <v>12.63626077287537</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.143351635235184</v>
+        <v>8.656555772994167</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>8.993950971028333</v>
+        <v>9.537169645740839</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.124658333996756</v>
+        <v>5.700366123463873</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.428836863619438</v>
+        <v>7.009573047937003</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>11.51732377538828</v>
+        <v>12.02319234234822</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>11.45634161886551</v>
+        <v>11.98621973321142</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>11.99531171142451</v>
+        <v>12.53225416609511</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.40172166427543</v>
+        <v>10.95825070486035</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>11.82498870551971</v>
+        <v>12.38628045592387</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>10.62125951566141</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>8.852795724654975</v>
+        <v>9.500441363978119</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>10.26418200868133</v>
+        <v>9.489888175113016</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>12.57456454306848</v>
+        <v>11.90671108995722</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.258224530862464</v>
+        <v>9.512973101642459</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>12.31001830190174</v>
+        <v>11.64285714285708</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>11.77172874880605</v>
+        <v>11.15360800190516</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>15.99067140589224</v>
+        <v>15.4263935207242</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>15.90596104662596</v>
+        <v>15.36573743149863</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.556539461662858</v>
+        <v>8.899904671115401</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>11.45634161886551</v>
+        <v>10.86293206197855</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.645638508810222</v>
+        <v>8.039103481163508</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.558584409373566</v>
+        <v>1.834963033627467</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.514531189179806</v>
+        <v>5.893129770992424</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.172811708415423</v>
+        <v>1.497971844428534</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.4377630449165153</v>
+        <v>-0.2529832935560279</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>34</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>9.28378985181859</v>
+        <v>9.254594057465958</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.672603758754803</v>
+        <v>7.671416972310148</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.395479432823251</v>
+        <v>1.39532604281893</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.408057517588162</v>
+        <v>7.407563025210159</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>12.75212090566894</v>
+        <v>12.80066682543471</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>13.04949493530385</v>
+        <v>13.07345234425347</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>10.02360810544963</v>
+        <v>10.07161978443995</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6.615362991074484</v>
+        <v>6.664610553468201</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.554380834551793</v>
+        <v>6.627637944331489</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.64563850881008</v>
+        <v>8.744985834104654</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.499760879961656</v>
+        <v>5.599668915980331</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.41649197349344</v>
+        <v>11.54018859452169</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.99634112018013</v>
+        <v>11.14503066795796</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>8.280900299818335</v>
+        <v>8.452899059384997</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>48</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>12.10241730279895</v>
+        <v>12.07322150844632</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.49123120973512</v>
+        <v>10.49004442329046</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>18.42979315831344</v>
+        <v>18.42963976830912</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>16.47668496856848</v>
+        <v>16.47619047619048</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>20.10506208213945</v>
+        <v>20.15360800190522</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>26.65243611177453</v>
+        <v>26.67639352072415</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>20.31772575250837</v>
+        <v>20.36573743149869</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>13.60065710872166</v>
+        <v>13.64990467111537</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>17.70634161886551</v>
+        <v>17.7795987286452</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>14.77308948920239</v>
+        <v>14.87243681449696</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>18.73505499760877</v>
+        <v>18.83496303362745</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.51943314996409</v>
+        <v>12.64312977099234</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>16.26594896331741</v>
+        <v>16.41463851109524</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>16.4916846135439</v>
+        <v>16.66368337311057</v>
       </c>
     </row>
     <row r="32">
@@ -1927,98 +1927,98 @@
         <v>24</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5.85241730279904</v>
+        <v>5.823221508446409</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.241231209735155</v>
+        <v>4.240044423290499</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>12.17979315831344</v>
+        <v>12.17963976830912</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>12.3095238095238</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>15.93839541547272</v>
+        <v>15.98694133523849</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12.06910277844119</v>
+        <v>12.0930601873908</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>16.15105908584164</v>
+        <v>16.19907076483196</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.51732377538818</v>
+        <v>11.5665713377819</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>15.62300828553219</v>
+        <v>15.69626539531189</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>18.93975615586893</v>
+        <v>19.03910348116351</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>22.90172166427546</v>
+        <v>23.00162970029413</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>27.10276648329747</v>
+        <v>27.22646310432571</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>22.51594896331731</v>
+        <v>22.66463851109514</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>22.74168461354385</v>
+        <v>22.91368337311051</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.223</t>
+          <t>X ≈ 0.2229</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>22</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.609993060374741</v>
+        <v>6.58079726602211</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>9.544261512765452</v>
+        <v>9.543074726320796</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.604035582555909</v>
+        <v>4.603882192551588</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>22.91607890796241</v>
+        <v>22.91558441558441</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>13.28688026395769</v>
+        <v>13.33542618372346</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>18.12970883904727</v>
+        <v>18.15366624799688</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>18.04499847978116</v>
+        <v>18.09301015877148</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>17.57792983599442</v>
+        <v>17.62717739838813</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>17.51694767947158</v>
+        <v>17.59020478925128</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>16.66702888314178</v>
+        <v>16.76637620843636</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>25.55323681579068</v>
+        <v>25.65314485180936</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>16.49670587723697</v>
+        <v>16.62040249826521</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>16.07655502392345</v>
+        <v>16.22524457170127</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>20.84774521960465</v>
+        <v>21.01974397917132</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>21</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-19.14758269720102</v>
+        <v>-19.17677849155366</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>22.09837406687801</v>
+        <v>22.09718728043335</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.417888396408657</v>
+        <v>7.417735006404335</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>17.07192306380657</v>
+        <v>17.07142857142857</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>11.7717287488061</v>
+        <v>11.82027466857188</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>16.83100754034596</v>
+        <v>16.85496494929558</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>16.7462971810798</v>
+        <v>16.79430886007012</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>16.27922853729306</v>
+        <v>16.32847609968677</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>6.694436856960756</v>
+        <v>6.767693966740453</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>15.36832758444042</v>
+        <v>15.467674909735</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>5.639816902370704</v>
+        <v>5.739724938389379</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>5.674195054725963</v>
+        <v>5.797891675754208</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.77785372522214</v>
+        <v>14.92654327299997</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.00358937544858</v>
+        <v>15.17558813501524</v>
       </c>
     </row>
   </sheetData>
@@ -2210,1093 +2210,1093 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.1889</t>
+          <t>X &gt; -0.1888</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4088</v>
+        <v>4099</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2253686030776336</v>
+        <v>-0.2241196069881468</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.1164923675006193</v>
+        <v>-0.1161543928937192</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.3029262041326817</v>
+        <v>-0.3021120565083919</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2326854560288893</v>
+        <v>-0.2320515940618222</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1963779959664791</v>
+        <v>-0.1969275385037363</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.08096232572546569</v>
+        <v>-0.08127631127000967</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.0302595954769842</v>
+        <v>-0.03124259772683047</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.09316311599746996</v>
+        <v>-0.09400519490171177</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.03032972864644989</v>
+        <v>0.0286240697758231</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.04851363885241966</v>
+        <v>-0.05058698922395877</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.01952823387494362</v>
+        <v>-0.02169225647491402</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1180974123830651</v>
+        <v>-0.1205254350549438</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.08432005111157537</v>
+        <v>-0.08739400923000318</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.06490377523626023</v>
+        <v>-0.06854806545167946</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.174</t>
+          <t>X &gt; -0.1738</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4069</v>
+        <v>4080</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1781232818817244</v>
+        <v>-0.1768599314103199</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.159242530361233</v>
+        <v>-0.1587825561816487</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3202068416865558</v>
+        <v>-0.3193417358055939</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.2747655503495636</v>
+        <v>-0.2740132727907891</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2357912773504935</v>
+        <v>-0.2364629200805979</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.07217757475967801</v>
+        <v>-0.07262800569463224</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.003692386463221453</v>
+        <v>0.00239023306463082</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.0818582287016909</v>
+        <v>-0.0829636597706056</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.01795182996026767</v>
+        <v>0.01593083798833561</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.0327456855255619</v>
+        <v>-0.0353333454769853</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.07633989433618638</v>
+        <v>-0.07882584709748386</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1755435142461437</v>
+        <v>-0.1784037909870619</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.1396611922927775</v>
+        <v>-0.1432925515528325</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1457979784115224</v>
+        <v>-0.1500421170855049</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.159</t>
+          <t>X &gt; -0.1588</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4053</v>
+        <v>4064</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.1690616281733028</v>
+        <v>-0.1677031910876181</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1191623942008846</v>
+        <v>-0.1188041210340032</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.279196342998894</v>
+        <v>-0.2784379413023288</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.2586911902632565</v>
+        <v>-0.2579774177712366</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2174391487812812</v>
+        <v>-0.2183536970881477</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.02972345483467365</v>
+        <v>-0.03038447534657962</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.02215925004530561</v>
+        <v>0.02061338335326468</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.0618829257696305</v>
+        <v>-0.06324029202961867</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.010719330699132</v>
+        <v>-0.01295882030211004</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.03362318847411672</v>
+        <v>-0.03660939985904577</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.07658208325904781</v>
+        <v>-0.07947020954931361</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1516519301838457</v>
+        <v>-0.1550748527164387</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.1139638799649774</v>
+        <v>-0.1182643179330825</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1456827686421249</v>
+        <v>-0.1506210888316843</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.144</t>
+          <t>X &gt; -0.1438</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4020</v>
+        <v>4030</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2369289241619299</v>
+        <v>-0.2469409121983901</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.198252917248972</v>
+        <v>-0.2090731752580766</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3563847958749236</v>
+        <v>-0.3667596377784719</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2871694565762724</v>
+        <v>-0.2977369165488</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2659977341921476</v>
+        <v>-0.2784296311722727</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.05436627154224993</v>
+        <v>-0.06642470612082718</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.07312679546838297</v>
+        <v>0.05981719369834337</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.01707538989401058</v>
+        <v>0.003968100253104012</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.01948861679512248</v>
+        <v>0.005435159871986173</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.04632734313697995</v>
+        <v>-0.06104525458259502</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.01339143540138821</v>
+        <v>-0.02816615060262251</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1639333343720324</v>
+        <v>-0.1792908639282729</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.07275202317022433</v>
+        <v>-0.08922736172377199</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1314497148142948</v>
+        <v>-0.1487649312732131</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.129</t>
+          <t>X &gt; -0.1289</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3958</v>
+        <v>3968</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2774408353694042</v>
+        <v>-0.2619329753516979</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2633867583588838</v>
+        <v>-0.2490678045151995</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.5186195400992517</v>
+        <v>-0.5036139805389865</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4755999776680824</v>
+        <v>-0.4607124901242585</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3196921401948174</v>
+        <v>-0.307795065733707</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.03377165423655981</v>
+        <v>-0.02129259597605682</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.04660343220572116</v>
+        <v>0.05756133086975979</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.02220100377712697</v>
+        <v>0.03327155586622155</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.05084073569619818</v>
+        <v>0.06051575188541847</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.02793692843187046</v>
+        <v>-0.01930538087066935</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.03396941316042756</v>
+        <v>0.042467440577866</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1447082641772965</v>
+        <v>-0.1622858461361005</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.02025546541041479</v>
+        <v>-0.01424785826736041</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.007599536700318765</v>
+        <v>-0.002983293556091837</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.1141</t>
+          <t>X &gt; -0.1139</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3888</v>
+        <v>3899</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4173425878273491</v>
+        <v>-0.4139973054595814</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2203072518033053</v>
+        <v>-0.2195993165884786</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.5243190071990753</v>
+        <v>-0.5228325249560086</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5598294832871744</v>
+        <v>-0.5582173007345759</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.3658129499365046</v>
+        <v>-0.3683981393434976</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1827794939749481</v>
+        <v>-0.1840492742592161</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.09947578792809253</v>
+        <v>-0.1027725531403263</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.03891659441139694</v>
+        <v>-0.04247689098453122</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.04269319006167649</v>
+        <v>0.03711238984739396</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.02917033880835618</v>
+        <v>0.02168098564730059</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1215880225381198</v>
+        <v>0.1137944021564294</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.009487158519171146</v>
+        <v>-0.01868771170438066</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1248029960593016</v>
+        <v>0.1133564598131542</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.05649942835871968</v>
+        <v>0.04350298497686111</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.09907</t>
+          <t>X &gt; -0.09893</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3808</v>
+        <v>3818</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.4788223377837681</v>
+        <v>-0.4610384758919395</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1392225424463476</v>
+        <v>-0.1246205027321352</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.4413118429957947</v>
+        <v>-0.4520308158294668</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4278898524547401</v>
+        <v>-0.4386475593372126</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2708876165768217</v>
+        <v>-0.2866846555288021</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.01459544091499509</v>
+        <v>0.0003611108966481424</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.04904947465777099</v>
+        <v>0.05854788901502417</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1731531758427565</v>
+        <v>0.1823314493580241</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2578102787134071</v>
+        <v>0.2644491951200578</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.3143626616402457</v>
+        <v>0.3185383320269821</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.3868524261052499</v>
+        <v>0.3908384589088172</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3048662208302559</v>
+        <v>0.3067423364373951</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.5033909865955835</v>
+        <v>0.5024232715036945</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.5077910561209436</v>
+        <v>0.5044813476173005</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.08409</t>
+          <t>X &gt; -0.08396</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3722</v>
+        <v>3732</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3256282125959302</v>
+        <v>-0.3338768449136822</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1285241910861288</v>
+        <v>-0.1402974570513891</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4016873310159568</v>
+        <v>-0.4127549240054122</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3909463283232739</v>
+        <v>-0.4020386348018619</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2715125627278852</v>
+        <v>-0.2887870796237877</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1203520919788161</v>
+        <v>-0.135103805479055</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.02408134381970228</v>
+        <v>0.006015580736452364</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.08134380400060337</v>
+        <v>0.06309354216938345</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.196168110234801</v>
+        <v>0.1746794529338587</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3004646904905641</v>
+        <v>0.2757201835190202</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3793502996222244</v>
+        <v>0.3811477725832901</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.34838051838517</v>
+        <v>0.34733437731267</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5074880447033649</v>
+        <v>0.5030615845839108</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.5336423423635495</v>
+        <v>0.5262235660366201</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.06912</t>
+          <t>X &gt; -0.06899</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3598</v>
+        <v>3608</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1685371881084308</v>
+        <v>-0.1765023247489026</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1031824560081489</v>
+        <v>-0.1153883575566468</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2890347718611181</v>
+        <v>-0.3007876057352661</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2269366131018913</v>
+        <v>-0.2388454552633732</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3898090018638811</v>
+        <v>-0.4090129546886416</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2159776430784888</v>
+        <v>-0.2317923199838177</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.06368894929467928</v>
+        <v>-0.08377847444875641</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1503241453475894</v>
+        <v>0.1295670950223737</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.3822367062926588</v>
+        <v>0.3569813285160492</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.6027211753026478</v>
+        <v>0.572879782381726</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.635915869588807</v>
+        <v>0.6059406021680473</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.7416553721863437</v>
+        <v>0.7075342031253271</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.6985459810074772</v>
+        <v>0.6606207776510473</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.8012547450984755</v>
+        <v>0.7592118283951237</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.05414</t>
+          <t>X &gt; -0.05402</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3430</v>
+        <v>3441</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.002383417621324213</v>
+        <v>0.02685541199326735</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.03340630173592984</v>
+        <v>0.05404287650008399</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3746968155313652</v>
+        <v>-0.4110187753520265</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5775785973230043</v>
+        <v>-0.6136721664870208</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6059004069562164</v>
+        <v>-0.6519072375722814</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.1182154298194149</v>
+        <v>-0.1759286853716446</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.01250409910641537</v>
+        <v>-0.0624193174127754</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.3221355720510743</v>
+        <v>0.2845200557307308</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.4519748066384395</v>
+        <v>0.4217129037782499</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8413286660611945</v>
+        <v>0.8170425232535479</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.886234723795809</v>
+        <v>0.8616761579015701</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.024677905208883</v>
+        <v>0.9944948595778982</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.000112958265404</v>
+        <v>0.9645610367585817</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.096883836090079</v>
+        <v>1.055938531494768</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.03916</t>
+          <t>X &gt; -0.03905</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3203</v>
+        <v>3212</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1947573991191192</v>
+        <v>-0.1321199069510186</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.06410834443799018</v>
+        <v>-0.01990582546572739</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4731834025660362</v>
+        <v>-0.4279289201304834</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.4506415175815377</v>
+        <v>-0.4679082585118763</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5674161245853426</v>
+        <v>-0.5669024244875587</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3465517424764784</v>
+        <v>-0.3563640267392785</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.04052969920502392</v>
+        <v>-0.04353738954083752</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4131376322492102</v>
+        <v>0.3620895450649257</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4006475207774045</v>
+        <v>0.3873640569987771</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.7217954449241901</v>
+        <v>0.6839836554554992</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.8779121404659378</v>
+        <v>0.8533259343433173</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.054924569620908</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.9647629458392259</v>
+        <v>0.9520645926389335</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.021162186652454</v>
+        <v>1.032197279295708</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.02418</t>
+          <t>X &gt; -0.02407</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2934</v>
+        <v>2943</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.2390682044473991</v>
+        <v>-0.1857141323182674</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.2198195149025253</v>
+        <v>-0.1557464796287178</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.5806235083532201</v>
+        <v>-0.5311695129585559</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.4503983647648582</v>
+        <v>-0.4169254658385171</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.6645607517035685</v>
+        <v>-0.6160148319377967</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.586686933772711</v>
+        <v>-0.5810818445493808</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.3470141318847055</v>
+        <v>-0.3359275362213268</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.224806768585573</v>
+        <v>0.2176076952403889</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1146154081362525</v>
+        <v>0.1126772199805899</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.406740498959536</v>
+        <v>0.4101534301951659</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6298456002645736</v>
+        <v>0.6137601793970973</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.024201542334694</v>
+        <v>1.011716247377002</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.032416879274223</v>
+        <v>1.024305517551205</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.8688148112262581</v>
+        <v>0.8656031828285435</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.009202</t>
+          <t>X &gt; -0.009103</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2557</v>
+        <v>2561</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2205886727790869</v>
+        <v>-0.1700182211428327</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2729283122185961</v>
+        <v>-0.2501363544439315</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.8235843423360691</v>
+        <v>-0.7399542988259213</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.6154168760664973</v>
+        <v>-0.5500362581580944</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.8208638437864764</v>
+        <v>-0.7659546689264829</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.126425042671642</v>
+        <v>-1.117925104812748</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.7431166811889796</v>
+        <v>-0.7490614751783937</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.3697876825386146</v>
+        <v>-0.4339492921802446</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1361642359354249</v>
+        <v>-0.1975911711335243</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3630283151817579</v>
+        <v>0.3061866518000329</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.6491174976087919</v>
+        <v>0.5706131702928374</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.174669570440869</v>
+        <v>1.097346873686625</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.167890584375499</v>
+        <v>1.053614171644469</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.064263156106811</v>
+        <v>1.029328303476319</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.005777</t>
+          <t>X &gt; 0.005868</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.1531385320244425</v>
+        <v>0.2180161149060496</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3293466064112209</v>
+        <v>0.400828737015992</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.6298650417492695</v>
+        <v>-0.5793056177549047</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.7348233412465177</v>
+        <v>-0.7537514299172372</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.9908927626394828</v>
+        <v>-0.9603816354004806</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.304995685026967</v>
+        <v>-1.299937143430355</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.9193391581219217</v>
+        <v>-0.8895616735413512</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.5611075971607207</v>
+        <v>-0.5546407834301164</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3139032022267685</v>
+        <v>-0.2618913011867861</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.4164400936928274</v>
+        <v>0.4686842630759571</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5211058929905121</v>
+        <v>0.5471627510085355</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.242323296121597</v>
+        <v>1.311876827045118</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.226640787216745</v>
+        <v>1.293544147772863</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.263697192160258</v>
+        <v>1.307073230231005</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.02076</t>
+          <t>X &gt; 0.02084</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1716</v>
+        <v>1720</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.003404526956942</v>
+        <v>1.001205644642901</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7278746475981066</v>
+        <v>0.7266878611534509</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.7702649136958399</v>
+        <v>-0.7973116165446399</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.4077517329413993</v>
+        <v>-0.4617940199335635</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.8298972674540508</v>
+        <v>-0.8347640911180392</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.345531367900264</v>
+        <v>-1.375932060671204</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.6172335970851321</v>
+        <v>-0.6226346615245717</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.05112195474138304</v>
+        <v>0.01618374088278074</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.545488905687229</v>
+        <v>0.5024669456994815</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.065992339696798</v>
+        <v>1.015847667210075</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.24378608026305</v>
+        <v>1.160544428976308</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.418239207040422</v>
+        <v>2.323362329131903</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.090541037909453</v>
+        <v>1.986343937451799</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.258001629860928</v>
+        <v>2.177249264583445</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.03573</t>
+          <t>X &gt; 0.03581</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.563464785500003</v>
+        <v>1.677432913838864</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.097590073968028</v>
+        <v>1.207570688811032</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.227746808281637</v>
+        <v>-0.1501093356335232</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2406855873847604</v>
+        <v>-0.1635944700460783</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6358112177889694</v>
+        <v>-0.5094744353707625</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.125838762957031</v>
+        <v>-1.096903970315282</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4231475474200508</v>
+        <v>-0.3690295935909234</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.5813161345095921</v>
+        <v>0.5988294022981435</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.27713014933147</v>
+        <v>1.278702671297545</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.256829326600695</v>
+        <v>1.243404556432381</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.026512284040955</v>
+        <v>1.971163750473352</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.74931820743538</v>
+        <v>2.674491778160828</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>2.659131326125909</v>
+        <v>2.56607220285148</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.237850441485442</v>
+        <v>2.169955774544263</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.05071</t>
+          <t>X &gt; 0.05078</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.007456062488899</v>
+        <v>1.06770570641892</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.9168424202300827</v>
+        <v>0.964902674558779</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.07484384406181022</v>
+        <v>0.1235371123855131</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2421582037630614</v>
+        <v>-0.1942064202583467</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.2437751271628841</v>
+        <v>-0.1463024725800111</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3936282889410307</v>
+        <v>-0.3211445276196372</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.8633429260325158</v>
+        <v>0.9610821047305578</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.916846733050782</v>
+        <v>2.017183095466279</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.891734039038603</v>
+        <v>2.964991148818299</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.758019360882422</v>
+        <v>2.857366686176995</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.359047835567615</v>
+        <v>3.458955871586291</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.163698382939032</v>
+        <v>4.233326727124862</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.653941794858596</v>
+        <v>3.748643285789335</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.162831566948931</v>
+        <v>3.281484029631024</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.06569</t>
+          <t>X &gt; 0.06575</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>922</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.508237982480829</v>
+        <v>2.479042188128197</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.391628895924597</v>
+        <v>3.390442109479942</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.888397641321404</v>
+        <v>2.888244251317083</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.476323435668981</v>
+        <v>2.475828943290978</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.938033882573286</v>
+        <v>1.986579802339058</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.801568432815749</v>
+        <v>1.825525841765362</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.018376511727453</v>
+        <v>3.066388190717774</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.635906566422278</v>
+        <v>3.685154128815995</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.551063238532912</v>
+        <v>4.624320348312608</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.677283270836455</v>
+        <v>4.776630596131028</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.774100550754135</v>
+        <v>5.87400858677281</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.784617531742867</v>
+        <v>6.908314152771112</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.930627199036827</v>
+        <v>6.079316746814655</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4.854844411085487</v>
+        <v>5.02684317065215</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.08067</t>
+          <t>X &gt; 0.08072</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>757</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.869150019663799</v>
+        <v>2.839954225311168</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.635771060021369</v>
+        <v>3.634584273576714</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.165702449374649</v>
+        <v>4.165549059370328</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.031726800360637</v>
+        <v>4.031232307982634</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.493437247264943</v>
+        <v>3.541983167030715</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.394510087996458</v>
+        <v>3.418467496946072</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.63080369174218</v>
+        <v>4.678815370732501</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.616839407268529</v>
+        <v>5.666086969662246</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6.480560024854071</v>
+        <v>6.553817134633768</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.159042813728966</v>
+        <v>6.25839013902354</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>7.275345618480664</v>
+        <v>7.375253654499339</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>8.234426544944306</v>
+        <v>8.35812316597255</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.946376087932094</v>
+        <v>8.095065635709922</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.586906982544356</v>
+        <v>6.758905742111018</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.09565</t>
+          <t>X &gt; 0.0957</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.148223042313326</v>
+        <v>3.211281209938889</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.351606485673344</v>
+        <v>4.281503793108079</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.619086756547439</v>
+        <v>4.716953201144946</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.080437727950375</v>
+        <v>5.178512200900251</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.211022347040107</v>
+        <v>4.357588101407707</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.177270548860619</v>
+        <v>4.298698661686004</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>6.244878070389163</v>
+        <v>6.39392980297464</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>6.274498168324271</v>
+        <v>6.425609480402237</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>6.710204753523357</v>
+        <v>6.886149309076387</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.019226354544486</v>
+        <v>7.057345603883299</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.973465593635282</v>
+        <v>8.014067511239418</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>9.001221229434314</v>
+        <v>9.067259124226204</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8.581070376120906</v>
+        <v>8.672101197662379</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.151176887274602</v>
+        <v>7.262771266974589</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.1106</t>
+          <t>X &gt; 0.1107</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>514</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.71752754923218</v>
+        <v>4.688331754879549</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.830076864728667</v>
+        <v>5.828890078284012</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.408068125888022</v>
+        <v>6.407914735883701</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6.927398327842148</v>
+        <v>6.926903835464145</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.610898658014932</v>
+        <v>5.659444577780704</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.491930275198662</v>
+        <v>6.515887684148275</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>8.352745207761281</v>
+        <v>8.400756886751601</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>7.885676563974542</v>
+        <v>7.934924126368259</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8.797457053366159</v>
+        <v>8.870714163145855</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.531195844584943</v>
+        <v>8.630543169879516</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>9.493809861422022</v>
+        <v>9.593717897440698</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>10.11184560132599</v>
+        <v>10.23554222235423</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>9.497142218829694</v>
+        <v>9.645831766607522</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.555562693958954</v>
+        <v>8.727561453525617</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>425</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.460260440053887</v>
+        <v>4.431064645701255</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.79025081757829</v>
+        <v>3.789064031133634</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.042538256352664</v>
+        <v>5.042384866348343</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.878645752882193</v>
+        <v>5.87815126050419</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.575650317433571</v>
+        <v>5.624196237199342</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.049494935303947</v>
+        <v>7.07345234425356</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.141255164273076</v>
+        <v>8.189266843263397</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.674186520486337</v>
+        <v>7.723434082880054</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.789674952198851</v>
+        <v>8.862932061978547</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>7.704462038221934</v>
+        <v>7.803809363516507</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.911525585844089</v>
+        <v>9.011433621862764</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>10.35766844408177</v>
+        <v>10.48136506511002</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>9.466929355474235</v>
+        <v>9.615618903252063</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>9.222076770406666</v>
+        <v>9.394075529973328</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>356</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.103353632386998</v>
+        <v>5.074157838034367</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.177560797750125</v>
+        <v>5.176374011305469</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.749081547826563</v>
+        <v>6.748928157822242</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.283801073437395</v>
+        <v>8.283306581059392</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>8.026410396746186</v>
+        <v>8.074956316511958</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>8.885582179190266</v>
+        <v>8.909539588139879</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>10.20536620194656</v>
+        <v>10.25337788093688</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>9.176499805350836</v>
+        <v>9.225747367744553</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>10.52001203085054</v>
+        <v>10.59326914063023</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.670093234520678</v>
+        <v>9.769440559815251</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.58898758187846</v>
+        <v>10.68889561789713</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>12.02786011625626</v>
+        <v>12.1515567372845</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.60770926294285</v>
+        <v>11.75639881072068</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>10.4289505311469</v>
+        <v>10.60094929071357</v>
       </c>
     </row>
     <row r="29">
@@ -3410,101 +3410,101 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.857112138479735</v>
+        <v>3.673633758151887</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.119165482035619</v>
+        <v>5.977382468049043</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.020168745167908</v>
+        <v>5.230287589274973</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.319407973263317</v>
+        <v>8.187026754164563</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.781118420167623</v>
+        <v>7.697777613212644</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>9.839055830084391</v>
+        <v>9.73734758432839</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>11.16279617504358</v>
+        <v>11.09011905694038</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.583051474918811</v>
+        <v>8.504144953800854</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>10.28263269867773</v>
+        <v>10.23395679696088</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.080601226291535</v>
+        <v>9.056771325686526</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.63646344831302</v>
+        <v>10.61941533044725</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>12.07929230489369</v>
+        <v>12.09100962964961</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>12.01125412763663</v>
+        <v>12.04920859354515</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.82853907363781</v>
+        <v>10.88482589372305</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.1705</t>
+          <t>X &gt; 0.1706</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>233</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.454706287062216</v>
+        <v>2.425510492709584</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>4.706181138204393</v>
+        <v>4.704994351759737</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.311409753449354</v>
+        <v>4.311256363445032</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7.445926742531285</v>
+        <v>7.445432250153281</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>6.90763718943559</v>
+        <v>6.956183109201362</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>8.492564867139336</v>
+        <v>8.516522276088949</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>10.12459270529807</v>
+        <v>10.17260438428839</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>8.369970413442651</v>
+        <v>8.419217975836368</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>10.02572645434478</v>
+        <v>10.09898356412447</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.175807658014918</v>
+        <v>9.275154983309491</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>12.4045828946045</v>
+        <v>12.50449093062318</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>13.29733014567227</v>
+        <v>13.42102676670051</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>14.16473294042754</v>
+        <v>14.31342248820537</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>13.10291494258539</v>
+        <v>13.27491370215206</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>199</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.287928190571172</v>
+        <v>1.258732396218541</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.199355162833974</v>
+        <v>4.198168376389319</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.80960890370708</v>
+        <v>4.809455513702758</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.452396861365798</v>
+        <v>7.451902368987795</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.90908218264196</v>
+        <v>5.957628102407732</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>7.713993900719259</v>
+        <v>7.737951309668873</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>10.14184635552344</v>
+        <v>10.18985803451376</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>8.669752586108558</v>
+        <v>8.719000148502275</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>10.61882068084206</v>
+        <v>10.69207779062176</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.266389321698142</v>
+        <v>9.365736646992715</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.58430122876457</v>
+        <v>13.68420926478325</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>13.6186793811199</v>
+        <v>13.74237600214814</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>14.7060662162487</v>
+        <v>14.85475576402653</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>13.9267767408471</v>
+        <v>14.09877550041376</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>151</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.149790202719778</v>
+        <v>-2.178985997072409</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.199288604878639</v>
+        <v>2.198101818433983</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.4800139088653239</v>
+        <v>0.4798605188610026</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.583748986228521</v>
+        <v>4.583254493850518</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.396452810616267</v>
+        <v>1.444998730382039</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.693826840251354</v>
+        <v>1.717784249200967</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.907129726018304</v>
+        <v>6.955141405008625</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>7.102312737860693</v>
+        <v>7.15156030025441</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.365833892596207</v>
+        <v>8.439091002375903</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>7.515915096266347</v>
+        <v>7.615262421560921</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>11.94697552741013</v>
+        <v>12.04688356342881</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>13.96810864665287</v>
+        <v>14.09180526768112</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>14.21020944896858</v>
+        <v>14.35889899674641</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>13.11144178793685</v>
+        <v>13.28344054750351</v>
       </c>
     </row>
     <row r="33">
@@ -3621,98 +3621,98 @@
         <v>127</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-3.662018392739078</v>
+        <v>-3.69121418709171</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1.813409687425441</v>
+        <v>1.812222900980785</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.730967996542198</v>
+        <v>-1.731121386546519</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.12366659586506</v>
+        <v>3.123172103487057</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.351630831246375</v>
+        <v>-1.303084911480603</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2668552268081399</v>
+        <v>-0.2428978178585268</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>5.160245437547744</v>
+        <v>5.208257116538064</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>6.267979943367301</v>
+        <v>6.317227505761018</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.994399361647673</v>
+        <v>7.06765647142737</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5.357078990514665</v>
+        <v>5.456426315809239</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>9.876787281073376</v>
+        <v>9.976695317092052</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>11.485968583035</v>
+        <v>11.60966520406324</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>12.64062087932788</v>
+        <v>12.78931042710571</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>11.29155337994812</v>
+        <v>11.46355213951478</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.2305</t>
+          <t>X &gt; 0.2304</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>105</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-5.814249363867688</v>
+        <v>-5.84344515822032</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1936121621161035</v>
+        <v>0.1924253756714478</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-3.058302079781797</v>
+        <v>-3.058455469786118</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.023315031431522</v>
+        <v>-1.023809523809526</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-4.418747441670078</v>
+        <v>-4.370201521904306</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-4.121373412034991</v>
+        <v>-4.097416003085378</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>2.460582895365505</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>3.898276156340678</v>
+        <v>3.947523718734395</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4.789674952198851</v>
+        <v>4.862932061978547</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.987375203488043</v>
+        <v>3.086722528782616</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.592197854751653</v>
+        <v>6.692105890770328</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.92071086807928</v>
+        <v>12.06940041585711</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>9.289303661162954</v>
+        <v>9.461302420729616</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-5.282578314074371</v>
+        <v>-5.283765100519027</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-5.67734969882941</v>
+        <v>-5.677503088833731</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-5.547124555241048</v>
+        <v>-5.547619047619051</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-8.466366489289122</v>
+        <v>-8.41782056952335</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-9.359468650130225</v>
+        <v>-9.335511241180612</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.110845676063065</v>
+        <v>-1.062833997072744</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.8030380611025834</v>
+        <v>0.8522856234963001</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>4.313484476008377</v>
+        <v>4.386741585788073</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1078628917500524</v>
+        <v>-0.008515566455479018</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>6.830293092846894</v>
+        <v>6.930201128865569</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>11.62657600710698</v>
+        <v>11.75027262813523</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>11.20642515379357</v>
+        <v>11.3551147015714</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>7.860732232591538</v>
+        <v>8.0327309921582</v>
       </c>
     </row>
   </sheetData>
@@ -3904,1093 +3904,1093 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.1889</t>
+          <t>X &lt; -0.1888</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.61432206470374</v>
+        <v>10.58512627035111</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>7.812659781163724</v>
+        <v>7.811472994719068</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>14.56074553926583</v>
+        <v>14.56059214926151</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>12.3100183019018</v>
+        <v>12.3095238095238</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.58125255832993</v>
+        <v>10.6297984780957</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.116721826060243</v>
+        <v>6.140679235009856</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4.841535276317892</v>
+        <v>4.889546955308212</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>7.945895203959722</v>
+        <v>7.995142766353439</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.123008285532187</v>
+        <v>3.196265395311883</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.034994251107086</v>
+        <v>7.13434157640166</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.639816902370704</v>
+        <v>5.739724938389379</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.825472772841195</v>
+        <v>8.974162320619023</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.860732232591538</v>
+        <v>8.0327309921582</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.174</t>
+          <t>X &lt; -0.1738</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>103</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6.742384940339427</v>
+        <v>6.713189145986796</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.0438202064989</v>
+        <v>8.042633420054244</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>12.50341775378271</v>
+        <v>12.50326436377838</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>11.6627691109633</v>
+        <v>11.6622746185853</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10.15360577145984</v>
+        <v>10.20215169122562</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4.625737082648314</v>
+        <v>4.649694491597927</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.599279150566616</v>
+        <v>2.647290829556937</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>6.015705652410944</v>
+        <v>6.06495321480466</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3.042102136664866</v>
+        <v>3.115359246444562</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>5.104804699558308</v>
+        <v>5.204152024852881</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.841851114113659</v>
+        <v>6.941759150132334</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>10.75972441210005</v>
+        <v>10.88342103312829</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>9.368699772378875</v>
+        <v>9.517389320156703</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.594435422605407</v>
+        <v>9.76643418217207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.159</t>
+          <t>X &lt; -0.1588</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>119</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.502277246776579</v>
+        <v>5.473081452423948</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>5.571763422620307</v>
+        <v>5.570576636175652</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.378672710134168</v>
+        <v>9.378519320129847</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.50889785372253</v>
+        <v>9.508403361344527</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8.130272166173057</v>
+        <v>8.178818085938829</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.545293254631673</v>
+        <v>2.569250663581286</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1.620246760911726</v>
+        <v>1.668258439902047</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.514522654940116</v>
+        <v>4.563770217333833</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.613204363963561</v>
+        <v>3.686461473743257</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>4.443957836541259</v>
+        <v>4.543305161835832</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>5.91992894718863</v>
+        <v>6.019836983207306</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8.475315502905296</v>
+        <v>8.599012123933541</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>7.214828515138102</v>
+        <v>7.363518062915929</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.28090029981842</v>
+        <v>8.452899059385082</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.144</t>
+          <t>X &lt; -0.1438</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.071715548413017</v>
+        <v>6.313417586877726</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6.434213665875504</v>
+        <v>6.691024815447356</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9.328915965330992</v>
+        <v>9.565260683341805</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.143351635235142</v>
+        <v>8.387955182072822</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7.605062082139447</v>
+        <v>7.898706041120903</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.639278217037685</v>
+        <v>2.942733390005188</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.07701108959690117</v>
+        <v>0.2676982158124162</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.429604477142675</v>
+        <v>1.762649769154557</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.026517057462002</v>
+        <v>2.379271931259588</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.808177208500574</v>
+        <v>4.16982243541193</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.945581313398264</v>
+        <v>3.312087216634012</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.927327886806225</v>
+        <v>7.291822581449878</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.533492822966501</v>
+        <v>4.935880341160569</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.075017946877246</v>
+        <v>6.492114745659592</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.129</t>
+          <t>X &lt; -0.1289</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.995719483484343</v>
+        <v>4.699190500694407</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.720981988551344</v>
+        <v>5.441594810887395</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9.531818080431826</v>
+        <v>9.233903334200598</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.194753504394015</v>
+        <v>8.89867109634551</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.320015353167484</v>
+        <v>6.083840560044749</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.477202466914719</v>
+        <v>1.24034700909624</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.4579126683962116</v>
+        <v>0.24945836173125</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.9254234638618115</v>
+        <v>0.7138581594874367</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.8644413073390353</v>
+        <v>0.6768855503506401</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.350971109140019</v>
+        <v>2.178638364884499</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.211690511627495</v>
+        <v>1.044265359208865</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.517096701365986</v>
+        <v>4.823362329131896</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>2.227786969547907</v>
+        <v>2.102623007219243</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.986232900148273</v>
+        <v>1.886551590164842</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.1141</t>
+          <t>X &lt; -0.1139</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>284</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.617675518761423</v>
+        <v>5.588479724408792</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.654376749641258</v>
+        <v>3.653189963196603</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7.132844801505932</v>
+        <v>7.132691411501611</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.967295297206967</v>
+        <v>7.966800804828964</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.316329687773248</v>
+        <v>5.36487560753902</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.148914985013974</v>
+        <v>3.172872393963587</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.359979273635126</v>
+        <v>2.407990952625447</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1.540797953792051</v>
+        <v>1.590045516185768</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7755904451566025</v>
+        <v>0.8488475549362988</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.9820096769957516</v>
+        <v>1.081357002290325</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.2790295094334496</v>
+        <v>-0.1791214734147744</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.515912023203562</v>
+        <v>1.639608644231807</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.312689534335199</v>
+        <v>-0.1639999865573714</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.6172714680040059</v>
+        <v>0.7892702275706682</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.09907</t>
+          <t>X &lt; -0.09893</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>4.936666387048064</v>
+        <v>4.750162147715756</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.951853920357863</v>
+        <v>1.797122048861276</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.579060557580846</v>
+        <v>4.691055293423283</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4.709285701169208</v>
+        <v>4.820939334637963</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.072095049172418</v>
+        <v>3.235799782727135</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.3474910568294831</v>
+        <v>0.4948866714090769</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.2627806975633149</v>
+        <v>0.160257979443891</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-1.028463770399256</v>
+        <v>-1.127492589158628</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.63889647637258</v>
+        <v>-1.712410403774875</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.214089997977162</v>
+        <v>-2.262266381850132</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.968241705687902</v>
+        <v>-3.014352034865674</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.109687729156761</v>
+        <v>-2.134267489281605</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.178190230821812</v>
+        <v>-4.17326103228379</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.22717985532055</v>
+        <v>-4.198188773008148</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.08409</t>
+          <t>X &lt; -0.08396</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.630195080576762</v>
+        <v>2.700531190634081</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.463453431957376</v>
+        <v>1.560813085522568</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.290904269424551</v>
+        <v>3.384369997429602</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.421129413012913</v>
+        <v>3.514254038644282</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.438395415472783</v>
+        <v>2.581545917648008</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.402436111774541</v>
+        <v>1.523954496333907</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4288368636194804</v>
+        <v>0.5763804470197513</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.03823178016725848</v>
+        <v>0.1105476866364086</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.765880603356706</v>
+        <v>-0.5916133925669129</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.615799399686566</v>
+        <v>-1.415441973381895</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.264945002391201</v>
+        <v>-2.284770890984497</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.008344627813649</v>
+        <v>-2.004874663597434</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.317384370015951</v>
+        <v>-3.286950550249955</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.536093164233868</v>
+        <v>-3.481364668278928</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.06912</t>
+          <t>X &lt; -0.06899</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.003404526956942</v>
+        <v>1.05510556641736</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.9601626847641924</v>
+        <v>1.037145872565858</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.784903495131104</v>
+        <v>1.860799188598982</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.56669658297033</v>
+        <v>1.642857142857146</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.596351280745722</v>
+        <v>2.718825393209563</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.674213115258858</v>
+        <v>1.774219607680671</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.8926386444944256</v>
+        <v>1.017911344542163</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.445510138665135</v>
+        <v>-0.3174866332324839</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.726004490309855</v>
+        <v>-1.571850546717108</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.098571370263414</v>
+        <v>-2.917418257966865</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.303272528523607</v>
+        <v>-3.121558705502956</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.965758487666534</v>
+        <v>-3.759044142051117</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.689045229481692</v>
+        <v>-3.458549894701889</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-4.334389718627975</v>
+        <v>-4.079070250077834</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.05414</t>
+          <t>X &lt; -0.05402</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>742</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.05504001975268125</v>
+        <v>-0.1674076749539211</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.08579545052580784</v>
+        <v>-0.0102902487309251</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.712587408088822</v>
+        <v>1.871741508603641</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.786208778092281</v>
+        <v>2.938707209791545</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.921773672435947</v>
+        <v>3.118802111677638</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.7932716912893625</v>
+        <v>1.056420330375623</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.4390195530474514</v>
+        <v>0.6677508543174824</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.106216206642252</v>
+        <v>-0.9334286622179917</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.571511031628638</v>
+        <v>-1.435856632503281</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.364826054373594</v>
+        <v>-3.265478729079021</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.569527212633787</v>
+        <v>-3.469619176615112</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-4.209003507717824</v>
+        <v>-4.08530688668958</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.090070803079747</v>
+        <v>-3.94138125530192</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.538189600292569</v>
+        <v>-4.366190840725906</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.03916</t>
+          <t>X &lt; -0.03905</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.6118674746202899</v>
+        <v>0.4010219851232293</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.3970619630891221</v>
+        <v>0.2478755434811646</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.550278194433162</v>
+        <v>1.386313244645528</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.577304163614912</v>
+        <v>1.618342331825474</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.96780718017866</v>
+        <v>1.946253558595721</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.336388640154304</v>
+        <v>1.356863868372415</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.426084885635305</v>
+        <v>0.4322676259715621</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.072975502217488</v>
+        <v>-0.8992756567535025</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.9275593099270552</v>
+        <v>-0.88065768161119</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.983876455070124</v>
+        <v>-1.85412033813828</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.498175136550131</v>
+        <v>-2.413752279836046</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.082992030634436</v>
+        <v>-3.020450475921209</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.780748663101605</v>
+        <v>-2.743016827044165</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.967809710501491</v>
+        <v>-3.008905023731167</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.02418</t>
+          <t>X &lt; -0.02407</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.5408406173302751</v>
+        <v>0.4122260454092483</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6659623925308509</v>
+        <v>0.5103940363142527</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.364619631275509</v>
+        <v>1.237552765373451</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.13608184525129</v>
+        <v>1.047180601624149</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.647873067599868</v>
+        <v>1.518700075564148</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.541369875910235</v>
+        <v>1.516137110467739</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.052782295319354</v>
+        <v>1.019305996053617</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.3028162353817621</v>
+        <v>-0.2846860190933285</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.0400788294201746</v>
+        <v>0.04365495354481652</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.648289078379797</v>
+        <v>-0.6554302808943078</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.176092013699758</v>
+        <v>-1.136879283347589</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.111019192523763</v>
+        <v>-2.081105333677527</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.127292824512452</v>
+        <v>-2.110408494008205</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.740006285756039</v>
+        <v>-1.736854261298028</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.009202</t>
+          <t>X &lt; -0.009103</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1615</v>
+        <v>1622</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.3294607452531721</v>
+        <v>0.2472411162894872</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5432501631756139</v>
+        <v>0.5022993252512791</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.295439416816841</v>
+        <v>1.150228003603246</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.027015001571776</v>
+        <v>0.9124649859943972</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.355062082139447</v>
+        <v>1.254159810611533</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.899960864249785</v>
+        <v>1.868111312135184</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.354877455294748</v>
+        <v>1.351004466489478</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.7639698022200818</v>
+        <v>0.8581356293463003</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.4553096271214514</v>
+        <v>0.5482424491942837</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3326896645644482</v>
+        <v>-0.2413393232644765</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7850688414004878</v>
+        <v>-0.6573446586802234</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.617563754060647</v>
+        <v>-1.488643628022416</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.604278074866315</v>
+        <v>-1.418848857974417</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.440461929283742</v>
+        <v>-1.382453083938337</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.005777</t>
+          <t>X &lt; 0.005868</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2052</v>
+        <v>2060</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1739709115445507</v>
+        <v>-0.2395804239208061</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.2534237951239362</v>
+        <v>-0.3251729680138524</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6419548825072567</v>
+        <v>0.5854368697584036</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7989936585814519</v>
+        <v>0.8119392684610034</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.066132641750151</v>
+        <v>1.026010128536448</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.439437085484371</v>
+        <v>1.422525048770567</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.089766668241445</v>
+        <v>1.050304436820404</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.7201164365345818</v>
+        <v>0.7082299373302519</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.5130066618919855</v>
+        <v>0.4561524009615994</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.2394937223579987</v>
+        <v>-0.2922918676736472</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.3467764685383017</v>
+        <v>-0.3725018233768864</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.091745612822045</v>
+        <v>-1.160216494769031</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.073513611775979</v>
+        <v>-1.140553143441423</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.113091214916132</v>
+        <v>-1.15589591491532</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.02076</t>
+          <t>X &lt; 0.02084</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2456</v>
+        <v>2463</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.71477717547954</v>
+        <v>-0.710677938918522</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.4365375419572359</v>
+        <v>-0.4337660632979947</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.5314117415451918</v>
+        <v>0.5473443107002751</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3181483832026188</v>
+        <v>0.3537346196060227</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6154321512732466</v>
+        <v>0.6147730504489104</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.016756697616685</v>
+        <v>1.03141173197465</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5476809824635964</v>
+        <v>0.5479236663164926</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.08061233867685758</v>
+        <v>0.1044409206090648</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2245700620461619</v>
+        <v>-0.1937940320246909</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.5860883699755348</v>
+        <v>-0.5494656311185651</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7093894468356439</v>
+        <v>-0.6500329112224819</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.529712149181172</v>
+        <v>-1.461839803044143</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.298662351293935</v>
+        <v>-1.226054129597429</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.416838730647186</v>
+        <v>-1.360575660588168</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.03573</t>
+          <t>X &lt; 0.03581</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2781</v>
+        <v>2788</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.7951197608069478</v>
+        <v>-0.8488042150263198</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.486074136515299</v>
+        <v>-0.5384478953947465</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1075270659468543</v>
+        <v>0.06817138674428236</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.149635297712706</v>
+        <v>0.1103339119779463</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.3493149557026598</v>
+        <v>0.2841049629348902</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.6306071502222466</v>
+        <v>0.6123734921118498</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.314131216203549</v>
+        <v>0.2852365370443053</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1888827906313608</v>
+        <v>-0.19673097670141</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5014824884913054</v>
+        <v>-0.500476459324716</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.4887125716651539</v>
+        <v>-0.4809538254266883</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.8731405451661871</v>
+        <v>-0.8443633726785151</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.234161386340695</v>
+        <v>-1.19647596377466</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.187022520027938</v>
+        <v>-1.141683946177409</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.9773013627236153</v>
+        <v>-0.9445184442017123</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.05071</t>
+          <t>X &lt; 0.05078</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3056</v>
+        <v>3066</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.377883751434247</v>
+        <v>-0.3983509411962771</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2760551568662777</v>
+        <v>-0.2921193193995677</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.03336616740705978</v>
+        <v>-0.05088780183496056</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.1146310086032827</v>
+        <v>0.0966932937023941</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1164887879833927</v>
+        <v>0.08043727019790481</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.2032199132115053</v>
+        <v>0.1759055571587567</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.2229472301770272</v>
+        <v>-0.257432109666297</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6068592311476593</v>
+        <v>-0.6404599122179917</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.9292792961671665</v>
+        <v>-0.9527631513070318</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.8788120036602649</v>
+        <v>-0.91203658398301</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.098169332018408</v>
+        <v>-1.130823867643301</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.390802298041116</v>
+        <v>-1.41325875573515</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.204201511003845</v>
+        <v>-1.236296169917729</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.025767393436887</v>
+        <v>-1.067073313125569</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.06569</t>
+          <t>X &lt; 0.06575</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3250</v>
+        <v>3261</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7187339894678431</v>
+        <v>-0.708034854819779</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.9038740426662386</v>
+        <v>-0.9004994202780878</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.8223534224899893</v>
+        <v>-0.819545235765851</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.67566676967283</v>
+        <v>-0.6732541380967021</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5224310139022776</v>
+        <v>-0.5344653925901923</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.4539174793856944</v>
+        <v>-0.4591984034116763</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.7676288683083357</v>
+        <v>-0.7786934130545546</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.9417261836616575</v>
+        <v>-0.9525593631668698</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.170386491733559</v>
+        <v>-1.187282267476441</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.204681459373788</v>
+        <v>-1.228890393262162</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.515482967346628</v>
+        <v>-1.538811476176448</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.80252256959308</v>
+        <v>-1.831663364159333</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.559976392983245</v>
+        <v>-1.597061877214621</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.255751283891982</v>
+        <v>-1.300514725632141</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.08067</t>
+          <t>X &lt; 0.08072</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3415</v>
+        <v>3426</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.6431097294841805</v>
+        <v>-0.6345666082542394</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7509874460376267</v>
+        <v>-0.7483209053889652</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.9258694219550847</v>
+        <v>-0.9228721122068322</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.867597269874345</v>
+        <v>-0.8647097954432112</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.747741656178313</v>
+        <v>-0.7561445454019164</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.6974762458065413</v>
+        <v>-0.700572117016101</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.9417716174507262</v>
+        <v>-0.9494387992033282</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.159281505718603</v>
+        <v>-1.166528895318216</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.321436158912263</v>
+        <v>-1.333512123390157</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.248895496660985</v>
+        <v>-1.267018967816028</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.49607431778032</v>
+        <v>-1.513535070776136</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.709056753459933</v>
+        <v>-1.731140940792933</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.644862902412513</v>
+        <v>-1.672731394555989</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.34445496673915</v>
+        <v>-1.37849409332258</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.09565</t>
+          <t>X &lt; 0.0957</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3568</v>
+        <v>3580</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.5401173709420632</v>
+        <v>-0.5479632025658034</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.6842808945479035</v>
+        <v>-0.6690127407778093</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7847220694037915</v>
+        <v>-0.7972468927880669</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.8351279623053784</v>
+        <v>-0.847393553521691</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.6875015186433302</v>
+        <v>-0.7087492006581684</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.6546108680912326</v>
+        <v>-0.6717112730328196</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.9759805411979272</v>
+        <v>-0.996124848958523</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.9803445700696471</v>
+        <v>-1.000820370713996</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.026166077747973</v>
+        <v>-1.05059652937431</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.077041156561023</v>
+        <v>-1.078084018836435</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.238341810008116</v>
+        <v>-1.238997334778887</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.412639679167526</v>
+        <v>-1.41675297607631</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.341107168185374</v>
+        <v>-1.34983603046674</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.099869945499435</v>
+        <v>-1.113318489086822</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.1106</t>
+          <t>X &lt; 0.1107</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3658</v>
+        <v>3669</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.6694205252224563</v>
+        <v>-0.663289445745221</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.7678514423992695</v>
+        <v>-0.7653888828763087</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.9027906519890863</v>
+        <v>-0.9000703766184159</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9487966744704224</v>
+        <v>-0.945889799246693</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.7634953217329326</v>
+        <v>-0.768088572319904</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.8605207894802334</v>
+        <v>-0.8613410454983139</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.094279704517554</v>
+        <v>-1.09780990256008</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.028163851977055</v>
+        <v>-1.032068118000304</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.128970966447064</v>
+        <v>-1.135979206393799</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.090282074606165</v>
+        <v>-1.101108879304718</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.225338337545523</v>
+        <v>-1.235843066590391</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.312534063150629</v>
+        <v>-1.326156527019073</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.22573820075295</v>
+        <v>-1.243172569740388</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.094200205118383</v>
+        <v>-1.115343609718536</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3747</v>
+        <v>3758</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5128309241513733</v>
+        <v>-0.5079903716915481</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.381008747700335</v>
+        <v>-0.3797610585839521</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.5752183726427447</v>
+        <v>-0.5735219898937558</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.6435794267824235</v>
+        <v>-0.6416439187139886</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.6084629444846215</v>
+        <v>-0.6122534262869834</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.7493614914212117</v>
+        <v>-0.7499208712036278</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8463658830803311</v>
+        <v>-0.8494020107323905</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.7928281031089099</v>
+        <v>-0.7961633416370475</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.8926278196561555</v>
+        <v>-0.8984285545508186</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.7683216900387677</v>
+        <v>-0.7774834406865097</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.9049450023912016</v>
+        <v>-0.9137740043943268</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.069190483004668</v>
+        <v>-1.080274484326786</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.9676867535093692</v>
+        <v>-0.981943026547782</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9405945431147487</v>
+        <v>-0.9576134159616245</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3816</v>
+        <v>3827</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.4830053488942383</v>
+        <v>-0.4788618248869909</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4348398456462448</v>
+        <v>-0.4334816685736982</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.632679622803181</v>
+        <v>-0.6308518071642126</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7497482079431137</v>
+        <v>-0.7475520309765855</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.7250032773376773</v>
+        <v>-0.727518171191754</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.7795722564262988</v>
+        <v>-0.779603871713924</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.8763626597333314</v>
+        <v>-0.8783940239003769</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7799028075525811</v>
+        <v>-0.7823285665574957</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.8789981700204663</v>
+        <v>-0.8834144933450432</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.7984637394189633</v>
+        <v>-0.8055845898361724</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.8839552144886085</v>
+        <v>-0.8908855303412011</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.018413890371129</v>
+        <v>-1.027214966537016</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.9787239910097583</v>
+        <v>-0.990011436658186</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.869426497567197</v>
+        <v>-0.8832419818236659</v>
       </c>
     </row>
     <row r="29">
@@ -5104,101 +5104,101 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3888</v>
+        <v>3900</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.2891703243051751</v>
+        <v>-0.2739758678207949</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.3997944312904878</v>
+        <v>-0.3867449427626752</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3704333955037669</v>
+        <v>-0.3832171310346126</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5854836649187831</v>
+        <v>-0.5719766167336502</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5454383027720269</v>
+        <v>-0.5358266361096184</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.6704591654328595</v>
+        <v>-0.6585604199104509</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.7413243116764789</v>
+        <v>-0.731011992611883</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5525272775136045</v>
+        <v>-0.5430036750188023</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6508593401206966</v>
+        <v>-0.6428297818114714</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5617854679747865</v>
+        <v>-0.5561834040823328</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.6751223346965247</v>
+        <v>-0.6692644836669217</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.7806953847402482</v>
+        <v>-0.7762705365422349</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.7751712903896575</v>
+        <v>-0.772727976130291</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.689385345303819</v>
+        <v>-0.6888807294535226</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.1705</t>
+          <t>X &lt; 0.1706</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3939</v>
+        <v>3950</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1529808078622921</v>
+        <v>-0.150788080249086</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.2323197900117435</v>
+        <v>-0.231602892879792</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2590254070873996</v>
+        <v>-0.258296779700629</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4189426164741477</v>
+        <v>-0.4177489177489164</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3863259624400897</v>
+        <v>-0.3881954838234947</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4551772654740063</v>
+        <v>-0.4553649431464919</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5261667969087682</v>
+        <v>-0.5276161191710145</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.4218397227105655</v>
+        <v>-0.423654479541888</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4943007070303622</v>
+        <v>-0.4973713514222098</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.4426937553661077</v>
+        <v>-0.4474923711379049</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.6332859460746079</v>
+        <v>-0.6375894581509201</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.6862887480313162</v>
+        <v>-0.6918904719226049</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.73701211959294</v>
+        <v>-0.7439922153031659</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6747916494670037</v>
+        <v>-0.6833630403915407</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3973</v>
+        <v>3984</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.07248652727294314</v>
+        <v>-0.07078232776414239</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.1648750219670632</v>
+        <v>-0.164359981113904</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.24490563686728</v>
+        <v>-0.2442233939770659</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.352129158136691</v>
+        <v>-0.351133843622577</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.2741443467907416</v>
+        <v>-0.2758936259435174</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3398396983234306</v>
+        <v>-0.340139545408114</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.4360430917127474</v>
+        <v>-0.4373194464767565</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.3617078070863613</v>
+        <v>-0.3632532236214914</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.4340555656493095</v>
+        <v>-0.436641766048524</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.3649961700047868</v>
+        <v>-0.3691211928585005</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.5808403746246071</v>
+        <v>-0.5843998958934691</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.5827681078975147</v>
+        <v>-0.5875526173668959</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6366261079793816</v>
+        <v>-0.6425551317320597</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.5981509431303067</v>
+        <v>-0.6053929321103055</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4021</v>
+        <v>4032</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.07238094517214932</v>
+        <v>0.07332451627494407</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.03804806954412498</v>
+        <v>-0.03789820776786001</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.02258779406751188</v>
+        <v>-0.02252034381883306</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1517364322419112</v>
+        <v>-0.1513041634268788</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.03141434465955939</v>
+        <v>-0.03322693994086023</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.0182638137652944</v>
+        <v>-0.01915103373129057</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.188729063777636</v>
+        <v>-0.1900932196525886</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.195282796915329</v>
+        <v>-0.1966777954522598</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.2177766126297627</v>
+        <v>-0.2200503507041347</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1844674466154785</v>
+        <v>-0.1878539023845036</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3504320799259943</v>
+        <v>-0.3533888870664512</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.4264405761109415</v>
+        <v>-0.4301225839902756</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4349046750051784</v>
+        <v>-0.4395436527199834</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.3941439531476192</v>
+        <v>-0.3998086903814837</v>
       </c>
     </row>
     <row r="33">
@@ -5312,101 +5312,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4045</v>
+        <v>4056</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1065654874548017</v>
+        <v>0.1072388755308111</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.01273313173227564</v>
+        <v>-0.01265960817459444</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.04961564352054637</v>
+        <v>0.04948650218339878</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.07798005403736141</v>
+        <v>-0.07775279319795203</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.06312818968754641</v>
+        <v>0.06135707939599655</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.05331200617374066</v>
+        <v>0.05237777269265109</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.09194848243733844</v>
+        <v>-0.09328299675629381</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1258918915252281</v>
+        <v>-0.1271755849161735</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1239052947147243</v>
+        <v>-0.1259869234930093</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.07111072484229197</v>
+        <v>-0.07419701144727497</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2125734608892245</v>
+        <v>-0.2152956507775556</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.2631836031863557</v>
+        <v>-0.2665548026892424</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.2987651576251125</v>
+        <v>-0.3028662132495441</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2568732768557567</v>
+        <v>-0.2618590332010626</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.2305</t>
+          <t>X &lt; 0.2304</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4067</v>
+        <v>4078</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1416329890734929</v>
+        <v>0.142051460373338</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.0388123162154983</v>
+        <v>0.03874042981046699</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.07418583446189331</v>
+        <v>0.07399046530105124</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.04609875321405354</v>
+        <v>0.04598825831701703</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1345027102061778</v>
+        <v>0.1328103508163991</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1509023694432514</v>
+        <v>0.1498394335973714</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.005992811909450779</v>
+        <v>0.004660320115576155</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.03026604374583997</v>
+        <v>-0.03153509382098463</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.02859616764398254</v>
+        <v>-0.03052862869008521</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.0193434808505657</v>
+        <v>0.01656550958101377</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.07329881074500832</v>
+        <v>-0.07584314132964209</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.1725673415571407</v>
+        <v>-0.1754976799880268</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2102063955813378</v>
+        <v>-0.2137221982289716</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1427101082002054</v>
+        <v>-0.1470490120455494</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4088</v>
+        <v>4099</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.04285865856586923</v>
+        <v>0.04339012063830694</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1518003154262146</v>
+        <v>0.1514204064251743</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1118090971603181</v>
+        <v>0.1115132476278546</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.1333467548056646</v>
+        <v>0.1330007301046479</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1941516598792603</v>
+        <v>0.1925563952839937</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2364204867745343</v>
+        <v>0.2352564376951705</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.09184052662314457</v>
+        <v>0.09053041737301015</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.05339281951791719</v>
+        <v>0.05215802068903486</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.005897771646687033</v>
+        <v>0.004257598040929622</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.09811392712998668</v>
+        <v>0.09564747336438728</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.04397213512158515</v>
+        <v>-0.04607060849831157</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.1425472901336775</v>
+        <v>-0.144909731567985</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.1332317654671584</v>
+        <v>-0.1361744970348795</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.06490377523626023</v>
+        <v>-0.06854806545167946</v>
       </c>
     </row>
   </sheetData>
